--- a/sentiment_analysis/manual_labeling_sample_LABELED_COMPLETE.xlsx
+++ b/sentiment_analysis/manual_labeling_sample_LABELED_COMPLETE.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lunlun/Downloads/Github/textmining_grp6/datasets/final/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lunlun/Downloads/Github/textmining_grp6/sentiment_analysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB59B060-4AD2-0E4E-9026-08FD33D742B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89E8C869-7D0D-324D-BEA6-C5A79DF81DF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="36000" windowHeight="22600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4420" yWindow="780" windowWidth="31580" windowHeight="20800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -4133,7 +4133,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4152,8 +4152,15 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF9C5700"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -4162,26 +4169,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor rgb="FFFFC7CE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
-        <bgColor rgb="FFFFEB9C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor rgb="FFC6EFCE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD9D9D9"/>
-        <bgColor rgb="FFD9D9D9"/>
       </patternFill>
     </fill>
   </fills>
@@ -4209,25 +4197,26 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Neutral" xfId="1" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -4536,33 +4525,33 @@
     <col min="3" max="4" width="13" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
     <col min="6" max="6" width="9" customWidth="1"/>
-    <col min="7" max="7" width="76.1640625" style="6" customWidth="1"/>
+    <col min="7" max="7" width="76.1640625" style="1" customWidth="1"/>
     <col min="8" max="8" width="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
     </row>
@@ -4585,10 +4574,10 @@
       <c r="F2" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -4611,10 +4600,10 @@
       <c r="F3" t="s">
         <v>12</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -4637,7 +4626,7 @@
       <c r="F4" t="s">
         <v>24</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="G4" s="1" t="s">
         <v>25</v>
       </c>
       <c r="H4" s="4" t="s">
@@ -4663,11 +4652,11 @@
       <c r="F5" t="s">
         <v>12</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="G5" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="H5" s="2" t="s">
-        <v>14</v>
+      <c r="H5" s="5" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="32" x14ac:dyDescent="0.2">
@@ -4689,7 +4678,7 @@
       <c r="F6" t="s">
         <v>34</v>
       </c>
-      <c r="G6" s="6" t="s">
+      <c r="G6" s="1" t="s">
         <v>35</v>
       </c>
       <c r="H6" s="4" t="s">
@@ -4715,10 +4704,10 @@
       <c r="F7" t="s">
         <v>12</v>
       </c>
-      <c r="G7" s="6" t="s">
+      <c r="G7" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="H7" s="3" t="s">
+      <c r="H7" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -4741,10 +4730,10 @@
       <c r="F8" t="s">
         <v>43</v>
       </c>
-      <c r="G8" s="6" t="s">
+      <c r="G8" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="H8" s="3" t="s">
+      <c r="H8" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -4767,10 +4756,10 @@
       <c r="F9" t="s">
         <v>34</v>
       </c>
-      <c r="G9" s="6" t="s">
+      <c r="G9" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="H9" s="3" t="s">
+      <c r="H9" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -4793,10 +4782,10 @@
       <c r="F10" t="s">
         <v>12</v>
       </c>
-      <c r="G10" s="6" t="s">
+      <c r="G10" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="H10" s="3" t="s">
+      <c r="H10" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -4819,11 +4808,11 @@
       <c r="F11" t="s">
         <v>34</v>
       </c>
-      <c r="G11" s="6" t="s">
+      <c r="G11" s="1" t="s">
         <v>56</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="96" x14ac:dyDescent="0.2">
@@ -4845,7 +4834,7 @@
       <c r="F12" t="s">
         <v>34</v>
       </c>
-      <c r="G12" s="6" t="s">
+      <c r="G12" s="1" t="s">
         <v>60</v>
       </c>
       <c r="H12" s="4" t="s">
@@ -4871,10 +4860,10 @@
       <c r="F13" t="s">
         <v>24</v>
       </c>
-      <c r="G13" s="6" t="s">
+      <c r="G13" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="H13" s="3" t="s">
+      <c r="H13" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -4897,10 +4886,10 @@
       <c r="F14" t="s">
         <v>43</v>
       </c>
-      <c r="G14" s="6" t="s">
+      <c r="G14" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="H14" s="3" t="s">
+      <c r="H14" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -4923,10 +4912,10 @@
       <c r="F15" t="s">
         <v>12</v>
       </c>
-      <c r="G15" s="6" t="s">
+      <c r="G15" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="H15" s="2" t="s">
+      <c r="H15" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -4949,10 +4938,10 @@
       <c r="F16" t="s">
         <v>12</v>
       </c>
-      <c r="G16" s="6" t="s">
+      <c r="G16" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="H16" s="3" t="s">
+      <c r="H16" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -4975,7 +4964,7 @@
       <c r="F17" t="s">
         <v>43</v>
       </c>
-      <c r="G17" s="6" t="s">
+      <c r="G17" s="1" t="s">
         <v>80</v>
       </c>
       <c r="H17" s="4" t="s">
@@ -5001,10 +4990,10 @@
       <c r="F18" t="s">
         <v>34</v>
       </c>
-      <c r="G18" s="6" t="s">
+      <c r="G18" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="H18" s="3" t="s">
+      <c r="H18" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -5027,10 +5016,10 @@
       <c r="F19" t="s">
         <v>12</v>
       </c>
-      <c r="G19" s="6" t="s">
+      <c r="G19" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="H19" s="3" t="s">
+      <c r="H19" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -5053,10 +5042,10 @@
       <c r="F20" t="s">
         <v>12</v>
       </c>
-      <c r="G20" s="6" t="s">
+      <c r="G20" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="H20" s="3" t="s">
+      <c r="H20" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -5079,10 +5068,10 @@
       <c r="F21" t="s">
         <v>12</v>
       </c>
-      <c r="G21" s="6" t="s">
+      <c r="G21" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="H21" s="3" t="s">
+      <c r="H21" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -5105,10 +5094,10 @@
       <c r="F22" t="s">
         <v>12</v>
       </c>
-      <c r="G22" s="6" t="s">
+      <c r="G22" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="H22" s="3" t="s">
+      <c r="H22" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -5131,10 +5120,10 @@
       <c r="F23" t="s">
         <v>12</v>
       </c>
-      <c r="G23" s="6" t="s">
+      <c r="G23" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="H23" s="3" t="s">
+      <c r="H23" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -5157,10 +5146,10 @@
       <c r="F24" t="s">
         <v>12</v>
       </c>
-      <c r="G24" s="6" t="s">
+      <c r="G24" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="H24" s="3" t="s">
+      <c r="H24" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -5183,10 +5172,10 @@
       <c r="F25" t="s">
         <v>12</v>
       </c>
-      <c r="G25" s="6" t="s">
+      <c r="G25" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="H25" s="3" t="s">
+      <c r="H25" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -5209,10 +5198,10 @@
       <c r="F26" t="s">
         <v>12</v>
       </c>
-      <c r="G26" s="6" t="s">
+      <c r="G26" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="H26" s="3" t="s">
+      <c r="H26" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -5235,10 +5224,10 @@
       <c r="F27" t="s">
         <v>43</v>
       </c>
-      <c r="G27" s="6" t="s">
+      <c r="G27" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="H27" s="3" t="s">
+      <c r="H27" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -5261,10 +5250,10 @@
       <c r="F28" t="s">
         <v>12</v>
       </c>
-      <c r="G28" s="6" t="s">
+      <c r="G28" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="H28" s="3" t="s">
+      <c r="H28" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -5287,7 +5276,7 @@
       <c r="F29" t="s">
         <v>24</v>
       </c>
-      <c r="G29" s="6" t="s">
+      <c r="G29" s="1" t="s">
         <v>126</v>
       </c>
       <c r="H29" s="4" t="s">
@@ -5313,7 +5302,7 @@
       <c r="F30" t="s">
         <v>24</v>
       </c>
-      <c r="G30" s="6" t="s">
+      <c r="G30" s="1" t="s">
         <v>130</v>
       </c>
       <c r="H30" s="4" t="s">
@@ -5339,10 +5328,10 @@
       <c r="F31" t="s">
         <v>43</v>
       </c>
-      <c r="G31" s="6" t="s">
+      <c r="G31" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="H31" s="3" t="s">
+      <c r="H31" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -5365,10 +5354,10 @@
       <c r="F32" t="s">
         <v>12</v>
       </c>
-      <c r="G32" s="6" t="s">
+      <c r="G32" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="H32" s="3" t="s">
+      <c r="H32" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -5391,10 +5380,10 @@
       <c r="F33" t="s">
         <v>12</v>
       </c>
-      <c r="G33" s="6" t="s">
+      <c r="G33" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="H33" s="3" t="s">
+      <c r="H33" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -5417,10 +5406,10 @@
       <c r="F34" t="s">
         <v>24</v>
       </c>
-      <c r="G34" s="6" t="s">
+      <c r="G34" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="H34" s="3" t="s">
+      <c r="H34" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -5443,10 +5432,10 @@
       <c r="F35" t="s">
         <v>34</v>
       </c>
-      <c r="G35" s="6" t="s">
+      <c r="G35" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="H35" s="2" t="s">
+      <c r="H35" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -5469,10 +5458,10 @@
       <c r="F36" t="s">
         <v>43</v>
       </c>
-      <c r="G36" s="6" t="s">
+      <c r="G36" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="H36" s="3" t="s">
+      <c r="H36" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -5495,10 +5484,10 @@
       <c r="F37" t="s">
         <v>12</v>
       </c>
-      <c r="G37" s="6" t="s">
+      <c r="G37" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="H37" s="3" t="s">
+      <c r="H37" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -5521,10 +5510,10 @@
       <c r="F38" t="s">
         <v>34</v>
       </c>
-      <c r="G38" s="6" t="s">
+      <c r="G38" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="H38" s="3" t="s">
+      <c r="H38" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -5547,10 +5536,10 @@
       <c r="F39" t="s">
         <v>12</v>
       </c>
-      <c r="G39" s="6" t="s">
+      <c r="G39" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="H39" s="3" t="s">
+      <c r="H39" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -5573,10 +5562,10 @@
       <c r="F40" t="s">
         <v>43</v>
       </c>
-      <c r="G40" s="6" t="s">
+      <c r="G40" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="H40" s="3" t="s">
+      <c r="H40" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -5599,10 +5588,10 @@
       <c r="F41" t="s">
         <v>12</v>
       </c>
-      <c r="G41" s="6" t="s">
+      <c r="G41" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="H41" s="3" t="s">
+      <c r="H41" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -5625,10 +5614,10 @@
       <c r="F42" t="s">
         <v>24</v>
       </c>
-      <c r="G42" s="6" t="s">
+      <c r="G42" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="H42" s="2" t="s">
+      <c r="H42" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -5651,10 +5640,10 @@
       <c r="F43" t="s">
         <v>24</v>
       </c>
-      <c r="G43" s="6" t="s">
+      <c r="G43" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="H43" s="3" t="s">
+      <c r="H43" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -5677,10 +5666,10 @@
       <c r="F44" t="s">
         <v>12</v>
       </c>
-      <c r="G44" s="6" t="s">
+      <c r="G44" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="H44" s="3" t="s">
+      <c r="H44" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -5703,7 +5692,7 @@
       <c r="F45" t="s">
         <v>43</v>
       </c>
-      <c r="G45" s="6" t="s">
+      <c r="G45" s="1" t="s">
         <v>183</v>
       </c>
       <c r="H45" s="4" t="s">
@@ -5729,10 +5718,10 @@
       <c r="F46" t="s">
         <v>43</v>
       </c>
-      <c r="G46" s="6" t="s">
+      <c r="G46" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="H46" s="2" t="s">
+      <c r="H46" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -5755,10 +5744,10 @@
       <c r="F47" t="s">
         <v>24</v>
       </c>
-      <c r="G47" s="6" t="s">
+      <c r="G47" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="H47" s="3" t="s">
+      <c r="H47" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -5781,10 +5770,10 @@
       <c r="F48" t="s">
         <v>12</v>
       </c>
-      <c r="G48" s="6" t="s">
+      <c r="G48" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="H48" s="2" t="s">
+      <c r="H48" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -5807,10 +5796,10 @@
       <c r="F49" t="s">
         <v>24</v>
       </c>
-      <c r="G49" s="6" t="s">
+      <c r="G49" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="H49" s="3" t="s">
+      <c r="H49" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -5833,7 +5822,7 @@
       <c r="F50" t="s">
         <v>34</v>
       </c>
-      <c r="G50" s="6" t="s">
+      <c r="G50" s="1" t="s">
         <v>203</v>
       </c>
       <c r="H50" s="4" t="s">
@@ -5859,10 +5848,10 @@
       <c r="F51" t="s">
         <v>12</v>
       </c>
-      <c r="G51" s="6" t="s">
+      <c r="G51" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="H51" s="2" t="s">
+      <c r="H51" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -5885,11 +5874,11 @@
       <c r="F52" t="s">
         <v>12</v>
       </c>
-      <c r="G52" s="6" t="s">
+      <c r="G52" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="H52" s="2" t="s">
-        <v>14</v>
+      <c r="H52" s="4" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="53" spans="1:8" ht="32" x14ac:dyDescent="0.2">
@@ -5911,10 +5900,10 @@
       <c r="F53" t="s">
         <v>24</v>
       </c>
-      <c r="G53" s="6" t="s">
+      <c r="G53" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="H53" s="3" t="s">
+      <c r="H53" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -5937,10 +5926,10 @@
       <c r="F54" t="s">
         <v>24</v>
       </c>
-      <c r="G54" s="6" t="s">
+      <c r="G54" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="H54" s="3" t="s">
+      <c r="H54" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -5963,7 +5952,7 @@
       <c r="F55" t="s">
         <v>12</v>
       </c>
-      <c r="G55" s="6" t="s">
+      <c r="G55" s="1" t="s">
         <v>223</v>
       </c>
       <c r="H55" s="4" t="s">
@@ -5989,10 +5978,10 @@
       <c r="F56" t="s">
         <v>43</v>
       </c>
-      <c r="G56" s="6" t="s">
+      <c r="G56" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="H56" s="3" t="s">
+      <c r="H56" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -6015,7 +6004,7 @@
       <c r="F57" t="s">
         <v>12</v>
       </c>
-      <c r="G57" s="6" t="s">
+      <c r="G57" s="1" t="s">
         <v>230</v>
       </c>
       <c r="H57" s="4" t="s">
@@ -6041,11 +6030,11 @@
       <c r="F58" t="s">
         <v>12</v>
       </c>
-      <c r="G58" s="6" t="s">
+      <c r="G58" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="H58" s="3" t="s">
-        <v>19</v>
+      <c r="H58" s="4" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="59" spans="1:8" ht="32" x14ac:dyDescent="0.2">
@@ -6067,10 +6056,10 @@
       <c r="F59" t="s">
         <v>43</v>
       </c>
-      <c r="G59" s="6" t="s">
+      <c r="G59" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="H59" s="3" t="s">
+      <c r="H59" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -6093,10 +6082,10 @@
       <c r="F60" t="s">
         <v>12</v>
       </c>
-      <c r="G60" s="6" t="s">
+      <c r="G60" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="H60" s="3" t="s">
+      <c r="H60" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -6119,10 +6108,10 @@
       <c r="F61" t="s">
         <v>12</v>
       </c>
-      <c r="G61" s="6" t="s">
+      <c r="G61" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="H61" s="3" t="s">
+      <c r="H61" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -6145,7 +6134,7 @@
       <c r="F62" t="s">
         <v>34</v>
       </c>
-      <c r="G62" s="6" t="s">
+      <c r="G62" s="1" t="s">
         <v>250</v>
       </c>
       <c r="H62" s="4" t="s">
@@ -6171,10 +6160,10 @@
       <c r="F63" t="s">
         <v>34</v>
       </c>
-      <c r="G63" s="6" t="s">
+      <c r="G63" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="H63" s="3" t="s">
+      <c r="H63" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -6197,10 +6186,10 @@
       <c r="F64" t="s">
         <v>43</v>
       </c>
-      <c r="G64" s="6" t="s">
+      <c r="G64" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="H64" s="3" t="s">
+      <c r="H64" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -6223,10 +6212,10 @@
       <c r="F65" t="s">
         <v>12</v>
       </c>
-      <c r="G65" s="6" t="s">
+      <c r="G65" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="H65" s="3" t="s">
+      <c r="H65" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -6249,7 +6238,7 @@
       <c r="F66" t="s">
         <v>24</v>
       </c>
-      <c r="G66" s="6" t="s">
+      <c r="G66" s="1" t="s">
         <v>266</v>
       </c>
       <c r="H66" s="4" t="s">
@@ -6275,10 +6264,10 @@
       <c r="F67" t="s">
         <v>12</v>
       </c>
-      <c r="G67" s="6" t="s">
+      <c r="G67" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="H67" s="3" t="s">
+      <c r="H67" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -6301,10 +6290,10 @@
       <c r="F68" t="s">
         <v>12</v>
       </c>
-      <c r="G68" s="6" t="s">
+      <c r="G68" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="H68" s="3" t="s">
+      <c r="H68" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -6327,10 +6316,10 @@
       <c r="F69" t="s">
         <v>12</v>
       </c>
-      <c r="G69" s="6" t="s">
+      <c r="G69" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="H69" s="3" t="s">
+      <c r="H69" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -6353,10 +6342,10 @@
       <c r="F70" t="s">
         <v>24</v>
       </c>
-      <c r="G70" s="6" t="s">
+      <c r="G70" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="H70" s="3" t="s">
+      <c r="H70" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -6379,10 +6368,10 @@
       <c r="F71" t="s">
         <v>34</v>
       </c>
-      <c r="G71" s="6" t="s">
+      <c r="G71" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="H71" s="2" t="s">
+      <c r="H71" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -6405,10 +6394,10 @@
       <c r="F72" t="s">
         <v>12</v>
       </c>
-      <c r="G72" s="6" t="s">
+      <c r="G72" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="H72" s="3" t="s">
+      <c r="H72" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -6431,10 +6420,10 @@
       <c r="F73" t="s">
         <v>34</v>
       </c>
-      <c r="G73" s="6" t="s">
+      <c r="G73" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="H73" s="3" t="s">
+      <c r="H73" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -6457,10 +6446,10 @@
       <c r="F74" t="s">
         <v>43</v>
       </c>
-      <c r="G74" s="6" t="s">
+      <c r="G74" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="H74" s="2" t="s">
+      <c r="H74" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -6483,7 +6472,7 @@
       <c r="F75" t="s">
         <v>12</v>
       </c>
-      <c r="G75" s="6" t="s">
+      <c r="G75" s="1" t="s">
         <v>299</v>
       </c>
       <c r="H75" s="4" t="s">
@@ -6509,10 +6498,10 @@
       <c r="F76" t="s">
         <v>12</v>
       </c>
-      <c r="G76" s="6" t="s">
+      <c r="G76" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="H76" s="3" t="s">
+      <c r="H76" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -6535,10 +6524,10 @@
       <c r="F77" t="s">
         <v>12</v>
       </c>
-      <c r="G77" s="6" t="s">
+      <c r="G77" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="H77" s="3" t="s">
+      <c r="H77" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -6561,10 +6550,10 @@
       <c r="F78" t="s">
         <v>34</v>
       </c>
-      <c r="G78" s="6" t="s">
+      <c r="G78" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="H78" s="3" t="s">
+      <c r="H78" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -6587,10 +6576,10 @@
       <c r="F79" t="s">
         <v>12</v>
       </c>
-      <c r="G79" s="6" t="s">
+      <c r="G79" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="H79" s="2" t="s">
+      <c r="H79" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -6613,11 +6602,11 @@
       <c r="F80" t="s">
         <v>24</v>
       </c>
-      <c r="G80" s="6" t="s">
+      <c r="G80" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="H80" s="3" t="s">
-        <v>19</v>
+      <c r="H80" s="4" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="81" spans="1:8" ht="64" x14ac:dyDescent="0.2">
@@ -6639,10 +6628,10 @@
       <c r="F81" t="s">
         <v>34</v>
       </c>
-      <c r="G81" s="6" t="s">
+      <c r="G81" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="H81" s="3" t="s">
+      <c r="H81" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -6665,7 +6654,7 @@
       <c r="F82" t="s">
         <v>34</v>
       </c>
-      <c r="G82" s="6" t="s">
+      <c r="G82" s="1" t="s">
         <v>324</v>
       </c>
       <c r="H82" s="4" t="s">
@@ -6691,10 +6680,10 @@
       <c r="F83" t="s">
         <v>43</v>
       </c>
-      <c r="G83" s="6" t="s">
+      <c r="G83" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="H83" s="3" t="s">
+      <c r="H83" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -6717,11 +6706,11 @@
       <c r="F84" t="s">
         <v>43</v>
       </c>
-      <c r="G84" s="6" t="s">
+      <c r="G84" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="H84" s="3" t="s">
-        <v>19</v>
+      <c r="H84" s="4" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="85" spans="1:8" ht="32" x14ac:dyDescent="0.2">
@@ -6743,11 +6732,11 @@
       <c r="F85" t="s">
         <v>24</v>
       </c>
-      <c r="G85" s="6" t="s">
+      <c r="G85" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="H85" s="3" t="s">
-        <v>19</v>
+      <c r="H85" s="4" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="86" spans="1:8" ht="64" x14ac:dyDescent="0.2">
@@ -6769,10 +6758,10 @@
       <c r="F86" t="s">
         <v>12</v>
       </c>
-      <c r="G86" s="6" t="s">
+      <c r="G86" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="H86" s="3" t="s">
+      <c r="H86" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -6795,10 +6784,10 @@
       <c r="F87" t="s">
         <v>24</v>
       </c>
-      <c r="G87" s="6" t="s">
+      <c r="G87" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="H87" s="3" t="s">
+      <c r="H87" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -6821,10 +6810,10 @@
       <c r="F88" t="s">
         <v>43</v>
       </c>
-      <c r="G88" s="6" t="s">
+      <c r="G88" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="H88" s="2" t="s">
+      <c r="H88" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -6847,10 +6836,10 @@
       <c r="F89" t="s">
         <v>43</v>
       </c>
-      <c r="G89" s="6" t="s">
+      <c r="G89" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="H89" s="3" t="s">
+      <c r="H89" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -6873,10 +6862,10 @@
       <c r="F90" t="s">
         <v>34</v>
       </c>
-      <c r="G90" s="6" t="s">
+      <c r="G90" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="H90" s="3" t="s">
+      <c r="H90" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -6899,7 +6888,7 @@
       <c r="F91" t="s">
         <v>12</v>
       </c>
-      <c r="G91" s="6" t="s">
+      <c r="G91" s="1" t="s">
         <v>357</v>
       </c>
       <c r="H91" s="4" t="s">
@@ -6925,10 +6914,10 @@
       <c r="F92" t="s">
         <v>24</v>
       </c>
-      <c r="G92" s="6" t="s">
+      <c r="G92" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="H92" s="2" t="s">
+      <c r="H92" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -6951,10 +6940,10 @@
       <c r="F93" t="s">
         <v>12</v>
       </c>
-      <c r="G93" s="6" t="s">
+      <c r="G93" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="H93" s="3" t="s">
+      <c r="H93" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -6977,7 +6966,7 @@
       <c r="F94" t="s">
         <v>12</v>
       </c>
-      <c r="G94" s="6" t="s">
+      <c r="G94" s="1" t="s">
         <v>367</v>
       </c>
       <c r="H94" s="4" t="s">
@@ -7003,10 +6992,10 @@
       <c r="F95" t="s">
         <v>12</v>
       </c>
-      <c r="G95" s="6" t="s">
+      <c r="G95" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="H95" s="2" t="s">
+      <c r="H95" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -7029,10 +7018,10 @@
       <c r="F96" t="s">
         <v>24</v>
       </c>
-      <c r="G96" s="6" t="s">
+      <c r="G96" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="H96" s="3" t="s">
+      <c r="H96" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -7055,10 +7044,10 @@
       <c r="F97" t="s">
         <v>43</v>
       </c>
-      <c r="G97" s="6" t="s">
+      <c r="G97" s="1" t="s">
         <v>377</v>
       </c>
-      <c r="H97" s="3" t="s">
+      <c r="H97" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -7081,10 +7070,10 @@
       <c r="F98" t="s">
         <v>43</v>
       </c>
-      <c r="G98" s="6" t="s">
+      <c r="G98" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="H98" s="3" t="s">
+      <c r="H98" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -7107,11 +7096,11 @@
       <c r="F99" t="s">
         <v>12</v>
       </c>
-      <c r="G99" s="6" t="s">
+      <c r="G99" s="1" t="s">
         <v>384</v>
       </c>
       <c r="H99" s="4" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="100" spans="1:8" ht="16" x14ac:dyDescent="0.2">
@@ -7133,10 +7122,10 @@
       <c r="F100" t="s">
         <v>12</v>
       </c>
-      <c r="G100" s="6" t="s">
+      <c r="G100" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="H100" s="2" t="s">
+      <c r="H100" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -7159,10 +7148,10 @@
       <c r="F101" t="s">
         <v>24</v>
       </c>
-      <c r="G101" s="6" t="s">
+      <c r="G101" s="1" t="s">
         <v>392</v>
       </c>
-      <c r="H101" s="2" t="s">
+      <c r="H101" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -7185,10 +7174,10 @@
       <c r="F102" t="s">
         <v>24</v>
       </c>
-      <c r="G102" s="6" t="s">
+      <c r="G102" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="H102" s="2" t="s">
+      <c r="H102" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -7211,10 +7200,10 @@
       <c r="F103" t="s">
         <v>43</v>
       </c>
-      <c r="G103" s="6" t="s">
+      <c r="G103" s="1" t="s">
         <v>399</v>
       </c>
-      <c r="H103" s="3" t="s">
+      <c r="H103" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -7237,10 +7226,10 @@
       <c r="F104" t="s">
         <v>24</v>
       </c>
-      <c r="G104" s="6" t="s">
+      <c r="G104" s="1" t="s">
         <v>403</v>
       </c>
-      <c r="H104" s="3" t="s">
+      <c r="H104" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -7263,7 +7252,7 @@
       <c r="F105" t="s">
         <v>34</v>
       </c>
-      <c r="G105" s="6" t="s">
+      <c r="G105" s="1" t="s">
         <v>406</v>
       </c>
       <c r="H105" s="4" t="s">
@@ -7289,10 +7278,10 @@
       <c r="F106" t="s">
         <v>34</v>
       </c>
-      <c r="G106" s="6" t="s">
+      <c r="G106" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="H106" s="3" t="s">
+      <c r="H106" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -7315,10 +7304,10 @@
       <c r="F107" t="s">
         <v>24</v>
       </c>
-      <c r="G107" s="6" t="s">
+      <c r="G107" s="1" t="s">
         <v>414</v>
       </c>
-      <c r="H107" s="3" t="s">
+      <c r="H107" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -7341,10 +7330,10 @@
       <c r="F108" t="s">
         <v>12</v>
       </c>
-      <c r="G108" s="6" t="s">
+      <c r="G108" s="1" t="s">
         <v>418</v>
       </c>
-      <c r="H108" s="3" t="s">
+      <c r="H108" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -7367,7 +7356,7 @@
       <c r="F109" t="s">
         <v>34</v>
       </c>
-      <c r="G109" s="6" t="s">
+      <c r="G109" s="1" t="s">
         <v>422</v>
       </c>
       <c r="H109" s="4" t="s">
@@ -7393,10 +7382,10 @@
       <c r="F110" t="s">
         <v>43</v>
       </c>
-      <c r="G110" s="6" t="s">
+      <c r="G110" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="H110" s="3" t="s">
+      <c r="H110" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -7419,10 +7408,10 @@
       <c r="F111" t="s">
         <v>24</v>
       </c>
-      <c r="G111" s="6" t="s">
+      <c r="G111" s="1" t="s">
         <v>430</v>
       </c>
-      <c r="H111" s="3" t="s">
+      <c r="H111" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -7445,7 +7434,7 @@
       <c r="F112" t="s">
         <v>24</v>
       </c>
-      <c r="G112" s="6" t="s">
+      <c r="G112" s="1" t="s">
         <v>434</v>
       </c>
       <c r="H112" s="4" t="s">
@@ -7471,10 +7460,10 @@
       <c r="F113" t="s">
         <v>34</v>
       </c>
-      <c r="G113" s="6" t="s">
+      <c r="G113" s="1" t="s">
         <v>438</v>
       </c>
-      <c r="H113" s="3" t="s">
+      <c r="H113" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -7497,10 +7486,10 @@
       <c r="F114" t="s">
         <v>43</v>
       </c>
-      <c r="G114" s="6" t="s">
+      <c r="G114" s="1" t="s">
         <v>441</v>
       </c>
-      <c r="H114" s="2" t="s">
+      <c r="H114" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -7523,10 +7512,10 @@
       <c r="F115" t="s">
         <v>12</v>
       </c>
-      <c r="G115" s="6" t="s">
+      <c r="G115" s="1" t="s">
         <v>445</v>
       </c>
-      <c r="H115" s="3" t="s">
+      <c r="H115" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -7549,10 +7538,10 @@
       <c r="F116" t="s">
         <v>43</v>
       </c>
-      <c r="G116" s="6" t="s">
+      <c r="G116" s="1" t="s">
         <v>449</v>
       </c>
-      <c r="H116" s="2" t="s">
+      <c r="H116" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -7575,7 +7564,7 @@
       <c r="F117" t="s">
         <v>12</v>
       </c>
-      <c r="G117" s="6" t="s">
+      <c r="G117" s="1" t="s">
         <v>451</v>
       </c>
       <c r="H117" s="4" t="s">
@@ -7601,10 +7590,10 @@
       <c r="F118" t="s">
         <v>12</v>
       </c>
-      <c r="G118" s="6" t="s">
+      <c r="G118" s="1" t="s">
         <v>455</v>
       </c>
-      <c r="H118" s="3" t="s">
+      <c r="H118" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -7627,11 +7616,11 @@
       <c r="F119" t="s">
         <v>12</v>
       </c>
-      <c r="G119" s="6" t="s">
+      <c r="G119" s="1" t="s">
         <v>459</v>
       </c>
-      <c r="H119" s="3" t="s">
-        <v>19</v>
+      <c r="H119" s="4" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="120" spans="1:8" ht="32" x14ac:dyDescent="0.2">
@@ -7653,10 +7642,10 @@
       <c r="F120" t="s">
         <v>12</v>
       </c>
-      <c r="G120" s="6" t="s">
+      <c r="G120" s="1" t="s">
         <v>462</v>
       </c>
-      <c r="H120" s="3" t="s">
+      <c r="H120" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -7679,10 +7668,10 @@
       <c r="F121" t="s">
         <v>34</v>
       </c>
-      <c r="G121" s="6" t="s">
+      <c r="G121" s="1" t="s">
         <v>465</v>
       </c>
-      <c r="H121" s="3" t="s">
+      <c r="H121" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -7705,11 +7694,11 @@
       <c r="F122" t="s">
         <v>12</v>
       </c>
-      <c r="G122" s="6" t="s">
+      <c r="G122" s="1" t="s">
         <v>469</v>
       </c>
-      <c r="H122" s="2" t="s">
-        <v>14</v>
+      <c r="H122" s="4" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="123" spans="1:8" ht="48" x14ac:dyDescent="0.2">
@@ -7731,11 +7720,11 @@
       <c r="F123" t="s">
         <v>43</v>
       </c>
-      <c r="G123" s="6" t="s">
+      <c r="G123" s="1" t="s">
         <v>473</v>
       </c>
-      <c r="H123" s="2" t="s">
-        <v>14</v>
+      <c r="H123" s="4" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="124" spans="1:8" ht="48" x14ac:dyDescent="0.2">
@@ -7757,10 +7746,10 @@
       <c r="F124" t="s">
         <v>12</v>
       </c>
-      <c r="G124" s="6" t="s">
+      <c r="G124" s="1" t="s">
         <v>476</v>
       </c>
-      <c r="H124" s="2" t="s">
+      <c r="H124" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -7783,10 +7772,10 @@
       <c r="F125" t="s">
         <v>43</v>
       </c>
-      <c r="G125" s="6" t="s">
+      <c r="G125" s="1" t="s">
         <v>480</v>
       </c>
-      <c r="H125" s="3" t="s">
+      <c r="H125" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -7809,10 +7798,10 @@
       <c r="F126" t="s">
         <v>12</v>
       </c>
-      <c r="G126" s="6" t="s">
+      <c r="G126" s="1" t="s">
         <v>484</v>
       </c>
-      <c r="H126" s="3" t="s">
+      <c r="H126" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -7835,10 +7824,10 @@
       <c r="F127" t="s">
         <v>43</v>
       </c>
-      <c r="G127" s="6" t="s">
+      <c r="G127" s="1" t="s">
         <v>488</v>
       </c>
-      <c r="H127" s="3" t="s">
+      <c r="H127" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -7861,10 +7850,10 @@
       <c r="F128" t="s">
         <v>12</v>
       </c>
-      <c r="G128" s="6" t="s">
+      <c r="G128" s="1" t="s">
         <v>491</v>
       </c>
-      <c r="H128" s="3" t="s">
+      <c r="H128" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -7887,10 +7876,10 @@
       <c r="F129" t="s">
         <v>12</v>
       </c>
-      <c r="G129" s="6" t="s">
+      <c r="G129" s="1" t="s">
         <v>495</v>
       </c>
-      <c r="H129" s="3" t="s">
+      <c r="H129" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -7913,10 +7902,10 @@
       <c r="F130" t="s">
         <v>43</v>
       </c>
-      <c r="G130" s="6" t="s">
+      <c r="G130" s="1" t="s">
         <v>498</v>
       </c>
-      <c r="H130" s="2" t="s">
+      <c r="H130" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -7939,10 +7928,10 @@
       <c r="F131" t="s">
         <v>12</v>
       </c>
-      <c r="G131" s="6" t="s">
+      <c r="G131" s="1" t="s">
         <v>502</v>
       </c>
-      <c r="H131" s="3" t="s">
+      <c r="H131" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -7965,10 +7954,10 @@
       <c r="F132" t="s">
         <v>43</v>
       </c>
-      <c r="G132" s="6" t="s">
+      <c r="G132" s="1" t="s">
         <v>506</v>
       </c>
-      <c r="H132" s="3" t="s">
+      <c r="H132" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -7991,10 +7980,10 @@
       <c r="F133" t="s">
         <v>12</v>
       </c>
-      <c r="G133" s="6" t="s">
+      <c r="G133" s="1" t="s">
         <v>510</v>
       </c>
-      <c r="H133" s="3" t="s">
+      <c r="H133" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -8017,10 +8006,10 @@
       <c r="F134" t="s">
         <v>43</v>
       </c>
-      <c r="G134" s="6" t="s">
+      <c r="G134" s="1" t="s">
         <v>513</v>
       </c>
-      <c r="H134" s="3" t="s">
+      <c r="H134" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -8043,10 +8032,10 @@
       <c r="F135" t="s">
         <v>43</v>
       </c>
-      <c r="G135" s="6" t="s">
+      <c r="G135" s="1" t="s">
         <v>515</v>
       </c>
-      <c r="H135" s="2" t="s">
+      <c r="H135" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -8069,10 +8058,10 @@
       <c r="F136" t="s">
         <v>43</v>
       </c>
-      <c r="G136" s="6" t="s">
+      <c r="G136" s="1" t="s">
         <v>518</v>
       </c>
-      <c r="H136" s="3" t="s">
+      <c r="H136" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -8095,11 +8084,11 @@
       <c r="F137" t="s">
         <v>34</v>
       </c>
-      <c r="G137" s="6" t="s">
+      <c r="G137" s="1" t="s">
         <v>522</v>
       </c>
-      <c r="H137" s="3" t="s">
-        <v>19</v>
+      <c r="H137" s="4" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="138" spans="1:8" ht="16" x14ac:dyDescent="0.2">
@@ -8121,10 +8110,10 @@
       <c r="F138" t="s">
         <v>12</v>
       </c>
-      <c r="G138" s="6" t="s">
+      <c r="G138" s="1" t="s">
         <v>526</v>
       </c>
-      <c r="H138" s="2" t="s">
+      <c r="H138" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -8147,7 +8136,7 @@
       <c r="F139" t="s">
         <v>43</v>
       </c>
-      <c r="G139" s="6" t="s">
+      <c r="G139" s="1" t="s">
         <v>530</v>
       </c>
       <c r="H139" s="4" t="s">
@@ -8173,7 +8162,7 @@
       <c r="F140" t="s">
         <v>24</v>
       </c>
-      <c r="G140" s="6" t="s">
+      <c r="G140" s="1" t="s">
         <v>534</v>
       </c>
       <c r="H140" s="4" t="s">
@@ -8199,10 +8188,10 @@
       <c r="F141" t="s">
         <v>34</v>
       </c>
-      <c r="G141" s="6" t="s">
+      <c r="G141" s="1" t="s">
         <v>536</v>
       </c>
-      <c r="H141" s="3" t="s">
+      <c r="H141" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -8225,10 +8214,10 @@
       <c r="F142" t="s">
         <v>12</v>
       </c>
-      <c r="G142" s="6" t="s">
+      <c r="G142" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H142" s="3" t="s">
+      <c r="H142" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -8251,10 +8240,10 @@
       <c r="F143" t="s">
         <v>24</v>
       </c>
-      <c r="G143" s="6" t="s">
+      <c r="G143" s="1" t="s">
         <v>542</v>
       </c>
-      <c r="H143" s="3" t="s">
+      <c r="H143" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -8277,10 +8266,10 @@
       <c r="F144" t="s">
         <v>43</v>
       </c>
-      <c r="G144" s="6" t="s">
+      <c r="G144" s="1" t="s">
         <v>545</v>
       </c>
-      <c r="H144" s="3" t="s">
+      <c r="H144" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -8303,10 +8292,10 @@
       <c r="F145" t="s">
         <v>34</v>
       </c>
-      <c r="G145" s="6" t="s">
+      <c r="G145" s="1" t="s">
         <v>548</v>
       </c>
-      <c r="H145" s="3" t="s">
+      <c r="H145" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -8329,10 +8318,10 @@
       <c r="F146" t="s">
         <v>43</v>
       </c>
-      <c r="G146" s="6" t="s">
+      <c r="G146" s="1" t="s">
         <v>552</v>
       </c>
-      <c r="H146" s="2" t="s">
+      <c r="H146" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -8355,10 +8344,10 @@
       <c r="F147" t="s">
         <v>24</v>
       </c>
-      <c r="G147" s="6" t="s">
+      <c r="G147" s="1" t="s">
         <v>555</v>
       </c>
-      <c r="H147" s="2" t="s">
+      <c r="H147" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -8381,10 +8370,10 @@
       <c r="F148" t="s">
         <v>43</v>
       </c>
-      <c r="G148" s="6" t="s">
+      <c r="G148" s="1" t="s">
         <v>559</v>
       </c>
-      <c r="H148" s="3" t="s">
+      <c r="H148" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -8407,7 +8396,7 @@
       <c r="F149" t="s">
         <v>12</v>
       </c>
-      <c r="G149" s="6" t="s">
+      <c r="G149" s="1" t="s">
         <v>561</v>
       </c>
       <c r="H149" s="4" t="s">
@@ -8433,10 +8422,10 @@
       <c r="F150" t="s">
         <v>12</v>
       </c>
-      <c r="G150" s="6" t="s">
+      <c r="G150" s="1" t="s">
         <v>564</v>
       </c>
-      <c r="H150" s="2" t="s">
+      <c r="H150" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -8459,10 +8448,10 @@
       <c r="F151" t="s">
         <v>43</v>
       </c>
-      <c r="G151" s="6" t="s">
+      <c r="G151" s="1" t="s">
         <v>568</v>
       </c>
-      <c r="H151" s="3" t="s">
+      <c r="H151" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -8485,10 +8474,10 @@
       <c r="F152" t="s">
         <v>43</v>
       </c>
-      <c r="G152" s="6" t="s">
+      <c r="G152" s="1" t="s">
         <v>572</v>
       </c>
-      <c r="H152" s="3" t="s">
+      <c r="H152" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -8511,10 +8500,10 @@
       <c r="F153" t="s">
         <v>24</v>
       </c>
-      <c r="G153" s="6" t="s">
+      <c r="G153" s="1" t="s">
         <v>575</v>
       </c>
-      <c r="H153" s="3" t="s">
+      <c r="H153" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -8537,10 +8526,10 @@
       <c r="F154" t="s">
         <v>12</v>
       </c>
-      <c r="G154" s="6" t="s">
+      <c r="G154" s="1" t="s">
         <v>578</v>
       </c>
-      <c r="H154" s="3" t="s">
+      <c r="H154" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -8563,10 +8552,10 @@
       <c r="F155" t="s">
         <v>24</v>
       </c>
-      <c r="G155" s="6" t="s">
+      <c r="G155" s="1" t="s">
         <v>582</v>
       </c>
-      <c r="H155" s="3" t="s">
+      <c r="H155" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -8589,7 +8578,7 @@
       <c r="F156" t="s">
         <v>12</v>
       </c>
-      <c r="G156" s="6" t="s">
+      <c r="G156" s="1" t="s">
         <v>586</v>
       </c>
       <c r="H156" s="4" t="s">
@@ -8615,10 +8604,10 @@
       <c r="F157" t="s">
         <v>34</v>
       </c>
-      <c r="G157" s="6" t="s">
+      <c r="G157" s="1" t="s">
         <v>590</v>
       </c>
-      <c r="H157" s="2" t="s">
+      <c r="H157" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -8641,7 +8630,7 @@
       <c r="F158" t="s">
         <v>12</v>
       </c>
-      <c r="G158" s="6" t="s">
+      <c r="G158" s="1" t="s">
         <v>593</v>
       </c>
       <c r="H158" s="4" t="s">
@@ -8667,10 +8656,10 @@
       <c r="F159" t="s">
         <v>43</v>
       </c>
-      <c r="G159" s="6" t="s">
+      <c r="G159" s="1" t="s">
         <v>596</v>
       </c>
-      <c r="H159" s="3" t="s">
+      <c r="H159" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -8693,10 +8682,10 @@
       <c r="F160" t="s">
         <v>34</v>
       </c>
-      <c r="G160" s="6" t="s">
+      <c r="G160" s="1" t="s">
         <v>599</v>
       </c>
-      <c r="H160" s="3" t="s">
+      <c r="H160" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -8719,10 +8708,10 @@
       <c r="F161" t="s">
         <v>34</v>
       </c>
-      <c r="G161" s="6" t="s">
+      <c r="G161" s="1" t="s">
         <v>603</v>
       </c>
-      <c r="H161" s="3" t="s">
+      <c r="H161" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -8745,10 +8734,10 @@
       <c r="F162" t="s">
         <v>12</v>
       </c>
-      <c r="G162" s="6" t="s">
+      <c r="G162" s="1" t="s">
         <v>607</v>
       </c>
-      <c r="H162" s="3" t="s">
+      <c r="H162" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -8771,10 +8760,10 @@
       <c r="F163" t="s">
         <v>12</v>
       </c>
-      <c r="G163" s="6" t="s">
+      <c r="G163" s="1" t="s">
         <v>611</v>
       </c>
-      <c r="H163" s="3" t="s">
+      <c r="H163" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -8797,7 +8786,7 @@
       <c r="F164" t="s">
         <v>43</v>
       </c>
-      <c r="G164" s="6" t="s">
+      <c r="G164" s="1" t="s">
         <v>615</v>
       </c>
       <c r="H164" s="4" t="s">
@@ -8823,10 +8812,10 @@
       <c r="F165" t="s">
         <v>43</v>
       </c>
-      <c r="G165" s="6" t="s">
+      <c r="G165" s="1" t="s">
         <v>619</v>
       </c>
-      <c r="H165" s="3" t="s">
+      <c r="H165" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -8849,10 +8838,10 @@
       <c r="F166" t="s">
         <v>12</v>
       </c>
-      <c r="G166" s="6" t="s">
+      <c r="G166" s="1" t="s">
         <v>622</v>
       </c>
-      <c r="H166" s="3" t="s">
+      <c r="H166" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -8875,7 +8864,7 @@
       <c r="F167" t="s">
         <v>43</v>
       </c>
-      <c r="G167" s="6" t="s">
+      <c r="G167" s="1" t="s">
         <v>626</v>
       </c>
       <c r="H167" s="4" t="s">
@@ -8901,10 +8890,10 @@
       <c r="F168" t="s">
         <v>43</v>
       </c>
-      <c r="G168" s="6" t="s">
+      <c r="G168" s="1" t="s">
         <v>630</v>
       </c>
-      <c r="H168" s="3" t="s">
+      <c r="H168" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -8927,10 +8916,10 @@
       <c r="F169" t="s">
         <v>24</v>
       </c>
-      <c r="G169" s="6" t="s">
+      <c r="G169" s="1" t="s">
         <v>633</v>
       </c>
-      <c r="H169" s="2" t="s">
+      <c r="H169" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -8953,10 +8942,10 @@
       <c r="F170" t="s">
         <v>43</v>
       </c>
-      <c r="G170" s="6" t="s">
+      <c r="G170" s="1" t="s">
         <v>637</v>
       </c>
-      <c r="H170" s="2" t="s">
+      <c r="H170" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -8979,10 +8968,10 @@
       <c r="F171" t="s">
         <v>34</v>
       </c>
-      <c r="G171" s="6" t="s">
+      <c r="G171" s="1" t="s">
         <v>641</v>
       </c>
-      <c r="H171" s="3" t="s">
+      <c r="H171" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -9005,10 +8994,10 @@
       <c r="F172" t="s">
         <v>12</v>
       </c>
-      <c r="G172" s="6" t="s">
+      <c r="G172" s="1" t="s">
         <v>644</v>
       </c>
-      <c r="H172" s="3" t="s">
+      <c r="H172" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -9031,11 +9020,11 @@
       <c r="F173" t="s">
         <v>24</v>
       </c>
-      <c r="G173" s="6" t="s">
+      <c r="G173" s="1" t="s">
         <v>648</v>
       </c>
       <c r="H173" s="4" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="174" spans="1:8" ht="48" x14ac:dyDescent="0.2">
@@ -9057,7 +9046,7 @@
       <c r="F174" t="s">
         <v>43</v>
       </c>
-      <c r="G174" s="6" t="s">
+      <c r="G174" s="1" t="s">
         <v>650</v>
       </c>
       <c r="H174" s="4" t="s">
@@ -9083,7 +9072,7 @@
       <c r="F175" t="s">
         <v>24</v>
       </c>
-      <c r="G175" s="6" t="s">
+      <c r="G175" s="1" t="s">
         <v>653</v>
       </c>
       <c r="H175" s="4" t="s">
@@ -9109,10 +9098,10 @@
       <c r="F176" t="s">
         <v>24</v>
       </c>
-      <c r="G176" s="6" t="s">
+      <c r="G176" s="1" t="s">
         <v>656</v>
       </c>
-      <c r="H176" s="3" t="s">
+      <c r="H176" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -9135,10 +9124,10 @@
       <c r="F177" t="s">
         <v>24</v>
       </c>
-      <c r="G177" s="6" t="s">
+      <c r="G177" s="1" t="s">
         <v>659</v>
       </c>
-      <c r="H177" s="3" t="s">
+      <c r="H177" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -9161,10 +9150,10 @@
       <c r="F178" t="s">
         <v>12</v>
       </c>
-      <c r="G178" s="6" t="s">
+      <c r="G178" s="1" t="s">
         <v>662</v>
       </c>
-      <c r="H178" s="3" t="s">
+      <c r="H178" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -9187,10 +9176,10 @@
       <c r="F179" t="s">
         <v>12</v>
       </c>
-      <c r="G179" s="6" t="s">
+      <c r="G179" s="1" t="s">
         <v>665</v>
       </c>
-      <c r="H179" s="2" t="s">
+      <c r="H179" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -9213,7 +9202,7 @@
       <c r="F180" t="s">
         <v>24</v>
       </c>
-      <c r="G180" s="6" t="s">
+      <c r="G180" s="1" t="s">
         <v>669</v>
       </c>
       <c r="H180" s="4" t="s">
@@ -9239,7 +9228,7 @@
       <c r="F181" t="s">
         <v>12</v>
       </c>
-      <c r="G181" s="6" t="s">
+      <c r="G181" s="1" t="s">
         <v>673</v>
       </c>
       <c r="H181" s="4" t="s">
@@ -9265,10 +9254,10 @@
       <c r="F182" t="s">
         <v>12</v>
       </c>
-      <c r="G182" s="6" t="s">
+      <c r="G182" s="1" t="s">
         <v>676</v>
       </c>
-      <c r="H182" s="3" t="s">
+      <c r="H182" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -9291,10 +9280,10 @@
       <c r="F183" t="s">
         <v>12</v>
       </c>
-      <c r="G183" s="6" t="s">
+      <c r="G183" s="1" t="s">
         <v>679</v>
       </c>
-      <c r="H183" s="2" t="s">
+      <c r="H183" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -9317,10 +9306,10 @@
       <c r="F184" t="s">
         <v>12</v>
       </c>
-      <c r="G184" s="6" t="s">
+      <c r="G184" s="1" t="s">
         <v>682</v>
       </c>
-      <c r="H184" s="3" t="s">
+      <c r="H184" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -9343,10 +9332,10 @@
       <c r="F185" t="s">
         <v>34</v>
       </c>
-      <c r="G185" s="6" t="s">
+      <c r="G185" s="1" t="s">
         <v>686</v>
       </c>
-      <c r="H185" s="3" t="s">
+      <c r="H185" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -9369,7 +9358,7 @@
       <c r="F186" t="s">
         <v>43</v>
       </c>
-      <c r="G186" s="6" t="s">
+      <c r="G186" s="1" t="s">
         <v>690</v>
       </c>
       <c r="H186" s="4" t="s">
@@ -9395,10 +9384,10 @@
       <c r="F187" t="s">
         <v>43</v>
       </c>
-      <c r="G187" s="6" t="s">
+      <c r="G187" s="1" t="s">
         <v>694</v>
       </c>
-      <c r="H187" s="2" t="s">
+      <c r="H187" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -9421,10 +9410,10 @@
       <c r="F188" t="s">
         <v>12</v>
       </c>
-      <c r="G188" s="6" t="s">
+      <c r="G188" s="1" t="s">
         <v>698</v>
       </c>
-      <c r="H188" s="3" t="s">
+      <c r="H188" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -9447,7 +9436,7 @@
       <c r="F189" t="s">
         <v>43</v>
       </c>
-      <c r="G189" s="6" t="s">
+      <c r="G189" s="1" t="s">
         <v>701</v>
       </c>
       <c r="H189" s="4" t="s">
@@ -9473,10 +9462,10 @@
       <c r="F190" t="s">
         <v>12</v>
       </c>
-      <c r="G190" s="6" t="s">
+      <c r="G190" s="1" t="s">
         <v>703</v>
       </c>
-      <c r="H190" s="3" t="s">
+      <c r="H190" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -9499,11 +9488,11 @@
       <c r="F191" t="s">
         <v>34</v>
       </c>
-      <c r="G191" s="6" t="s">
+      <c r="G191" s="1" t="s">
         <v>707</v>
       </c>
       <c r="H191" s="4" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="192" spans="1:8" ht="16" x14ac:dyDescent="0.2">
@@ -9525,7 +9514,7 @@
       <c r="F192" t="s">
         <v>12</v>
       </c>
-      <c r="G192" s="6" t="s">
+      <c r="G192" s="1" t="s">
         <v>710</v>
       </c>
       <c r="H192" s="4" t="s">
@@ -9551,10 +9540,10 @@
       <c r="F193" t="s">
         <v>24</v>
       </c>
-      <c r="G193" s="6" t="s">
+      <c r="G193" s="1" t="s">
         <v>713</v>
       </c>
-      <c r="H193" s="2" t="s">
+      <c r="H193" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -9577,10 +9566,10 @@
       <c r="F194" t="s">
         <v>12</v>
       </c>
-      <c r="G194" s="6" t="s">
+      <c r="G194" s="1" t="s">
         <v>716</v>
       </c>
-      <c r="H194" s="3" t="s">
+      <c r="H194" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -9603,10 +9592,10 @@
       <c r="F195" t="s">
         <v>12</v>
       </c>
-      <c r="G195" s="6" t="s">
+      <c r="G195" s="1" t="s">
         <v>719</v>
       </c>
-      <c r="H195" s="3" t="s">
+      <c r="H195" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -9629,10 +9618,10 @@
       <c r="F196" t="s">
         <v>34</v>
       </c>
-      <c r="G196" s="6" t="s">
+      <c r="G196" s="1" t="s">
         <v>722</v>
       </c>
-      <c r="H196" s="3" t="s">
+      <c r="H196" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -9655,10 +9644,10 @@
       <c r="F197" t="s">
         <v>43</v>
       </c>
-      <c r="G197" s="6" t="s">
+      <c r="G197" s="1" t="s">
         <v>725</v>
       </c>
-      <c r="H197" s="3" t="s">
+      <c r="H197" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -9681,10 +9670,10 @@
       <c r="F198" t="s">
         <v>12</v>
       </c>
-      <c r="G198" s="6" t="s">
+      <c r="G198" s="1" t="s">
         <v>728</v>
       </c>
-      <c r="H198" s="3" t="s">
+      <c r="H198" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -9707,10 +9696,10 @@
       <c r="F199" t="s">
         <v>24</v>
       </c>
-      <c r="G199" s="6" t="s">
+      <c r="G199" s="1" t="s">
         <v>730</v>
       </c>
-      <c r="H199" s="3" t="s">
+      <c r="H199" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -9733,10 +9722,10 @@
       <c r="F200" t="s">
         <v>12</v>
       </c>
-      <c r="G200" s="6" t="s">
+      <c r="G200" s="1" t="s">
         <v>733</v>
       </c>
-      <c r="H200" s="3" t="s">
+      <c r="H200" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -9759,10 +9748,10 @@
       <c r="F201" t="s">
         <v>12</v>
       </c>
-      <c r="G201" s="6" t="s">
+      <c r="G201" s="1" t="s">
         <v>737</v>
       </c>
-      <c r="H201" s="3" t="s">
+      <c r="H201" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -9785,11 +9774,11 @@
       <c r="F202" t="s">
         <v>12</v>
       </c>
-      <c r="G202" s="6" t="s">
+      <c r="G202" s="1" t="s">
         <v>741</v>
       </c>
-      <c r="H202" s="3" t="s">
-        <v>19</v>
+      <c r="H202" s="4" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="203" spans="1:8" ht="48" x14ac:dyDescent="0.2">
@@ -9811,10 +9800,10 @@
       <c r="F203" t="s">
         <v>24</v>
       </c>
-      <c r="G203" s="6" t="s">
+      <c r="G203" s="1" t="s">
         <v>745</v>
       </c>
-      <c r="H203" s="2" t="s">
+      <c r="H203" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -9837,10 +9826,10 @@
       <c r="F204" t="s">
         <v>34</v>
       </c>
-      <c r="G204" s="6" t="s">
+      <c r="G204" s="1" t="s">
         <v>748</v>
       </c>
-      <c r="H204" s="3" t="s">
+      <c r="H204" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -9863,10 +9852,10 @@
       <c r="F205" t="s">
         <v>24</v>
       </c>
-      <c r="G205" s="6" t="s">
+      <c r="G205" s="1" t="s">
         <v>751</v>
       </c>
-      <c r="H205" s="2" t="s">
+      <c r="H205" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -9889,10 +9878,10 @@
       <c r="F206" t="s">
         <v>12</v>
       </c>
-      <c r="G206" s="6" t="s">
+      <c r="G206" s="1" t="s">
         <v>754</v>
       </c>
-      <c r="H206" s="3" t="s">
+      <c r="H206" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -9915,7 +9904,7 @@
       <c r="F207" t="s">
         <v>12</v>
       </c>
-      <c r="G207" s="6" t="s">
+      <c r="G207" s="1" t="s">
         <v>757</v>
       </c>
       <c r="H207" s="4" t="s">
@@ -9941,10 +9930,10 @@
       <c r="F208" t="s">
         <v>12</v>
       </c>
-      <c r="G208" s="6" t="s">
+      <c r="G208" s="1" t="s">
         <v>761</v>
       </c>
-      <c r="H208" s="3" t="s">
+      <c r="H208" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -9967,10 +9956,10 @@
       <c r="F209" t="s">
         <v>12</v>
       </c>
-      <c r="G209" s="6" t="s">
+      <c r="G209" s="1" t="s">
         <v>764</v>
       </c>
-      <c r="H209" s="3" t="s">
+      <c r="H209" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -9993,10 +9982,10 @@
       <c r="F210" t="s">
         <v>12</v>
       </c>
-      <c r="G210" s="6" t="s">
+      <c r="G210" s="1" t="s">
         <v>768</v>
       </c>
-      <c r="H210" s="3" t="s">
+      <c r="H210" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -10019,10 +10008,10 @@
       <c r="F211" t="s">
         <v>12</v>
       </c>
-      <c r="G211" s="6" t="s">
+      <c r="G211" s="1" t="s">
         <v>772</v>
       </c>
-      <c r="H211" s="3" t="s">
+      <c r="H211" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -10045,11 +10034,11 @@
       <c r="F212" t="s">
         <v>12</v>
       </c>
-      <c r="G212" s="6" t="s">
+      <c r="G212" s="1" t="s">
         <v>775</v>
       </c>
-      <c r="H212" s="3" t="s">
-        <v>19</v>
+      <c r="H212" s="4" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="213" spans="1:8" ht="32" x14ac:dyDescent="0.2">
@@ -10071,10 +10060,10 @@
       <c r="F213" t="s">
         <v>12</v>
       </c>
-      <c r="G213" s="6" t="s">
+      <c r="G213" s="1" t="s">
         <v>777</v>
       </c>
-      <c r="H213" s="3" t="s">
+      <c r="H213" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -10097,10 +10086,10 @@
       <c r="F214" t="s">
         <v>43</v>
       </c>
-      <c r="G214" s="6" t="s">
+      <c r="G214" s="1" t="s">
         <v>781</v>
       </c>
-      <c r="H214" s="3" t="s">
+      <c r="H214" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -10123,10 +10112,10 @@
       <c r="F215" t="s">
         <v>12</v>
       </c>
-      <c r="G215" s="6" t="s">
+      <c r="G215" s="1" t="s">
         <v>785</v>
       </c>
-      <c r="H215" s="3" t="s">
+      <c r="H215" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -10149,10 +10138,10 @@
       <c r="F216" t="s">
         <v>24</v>
       </c>
-      <c r="G216" s="6" t="s">
+      <c r="G216" s="1" t="s">
         <v>789</v>
       </c>
-      <c r="H216" s="3" t="s">
+      <c r="H216" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -10175,10 +10164,10 @@
       <c r="F217" t="s">
         <v>24</v>
       </c>
-      <c r="G217" s="6" t="s">
+      <c r="G217" s="1" t="s">
         <v>792</v>
       </c>
-      <c r="H217" s="2" t="s">
+      <c r="H217" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -10201,10 +10190,10 @@
       <c r="F218" t="s">
         <v>12</v>
       </c>
-      <c r="G218" s="6" t="s">
+      <c r="G218" s="1" t="s">
         <v>796</v>
       </c>
-      <c r="H218" s="3" t="s">
+      <c r="H218" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -10227,10 +10216,10 @@
       <c r="F219" t="s">
         <v>43</v>
       </c>
-      <c r="G219" s="6" t="s">
+      <c r="G219" s="1" t="s">
         <v>799</v>
       </c>
-      <c r="H219" s="3" t="s">
+      <c r="H219" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -10253,10 +10242,10 @@
       <c r="F220" t="s">
         <v>43</v>
       </c>
-      <c r="G220" s="6" t="s">
+      <c r="G220" s="1" t="s">
         <v>802</v>
       </c>
-      <c r="H220" s="3" t="s">
+      <c r="H220" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -10279,10 +10268,10 @@
       <c r="F221" t="s">
         <v>24</v>
       </c>
-      <c r="G221" s="6" t="s">
+      <c r="G221" s="1" t="s">
         <v>805</v>
       </c>
-      <c r="H221" s="3" t="s">
+      <c r="H221" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -10305,10 +10294,10 @@
       <c r="F222" t="s">
         <v>24</v>
       </c>
-      <c r="G222" s="6" t="s">
+      <c r="G222" s="1" t="s">
         <v>808</v>
       </c>
-      <c r="H222" s="3" t="s">
+      <c r="H222" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -10331,10 +10320,10 @@
       <c r="F223" t="s">
         <v>12</v>
       </c>
-      <c r="G223" s="6" t="s">
+      <c r="G223" s="1" t="s">
         <v>811</v>
       </c>
-      <c r="H223" s="3" t="s">
+      <c r="H223" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -10357,10 +10346,10 @@
       <c r="F224" t="s">
         <v>34</v>
       </c>
-      <c r="G224" s="6" t="s">
+      <c r="G224" s="1" t="s">
         <v>814</v>
       </c>
-      <c r="H224" s="2" t="s">
+      <c r="H224" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -10383,10 +10372,10 @@
       <c r="F225" t="s">
         <v>43</v>
       </c>
-      <c r="G225" s="6" t="s">
+      <c r="G225" s="1" t="s">
         <v>817</v>
       </c>
-      <c r="H225" s="3" t="s">
+      <c r="H225" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -10409,7 +10398,7 @@
       <c r="F226" t="s">
         <v>24</v>
       </c>
-      <c r="G226" s="6" t="s">
+      <c r="G226" s="1" t="s">
         <v>821</v>
       </c>
       <c r="H226" s="4" t="s">
@@ -10435,10 +10424,10 @@
       <c r="F227" t="s">
         <v>43</v>
       </c>
-      <c r="G227" s="6" t="s">
+      <c r="G227" s="1" t="s">
         <v>824</v>
       </c>
-      <c r="H227" s="2" t="s">
+      <c r="H227" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -10461,10 +10450,10 @@
       <c r="F228" t="s">
         <v>24</v>
       </c>
-      <c r="G228" s="6" t="s">
+      <c r="G228" s="1" t="s">
         <v>825</v>
       </c>
-      <c r="H228" s="2" t="s">
+      <c r="H228" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -10487,10 +10476,10 @@
       <c r="F229" t="s">
         <v>12</v>
       </c>
-      <c r="G229" s="6" t="s">
+      <c r="G229" s="1" t="s">
         <v>829</v>
       </c>
-      <c r="H229" s="3" t="s">
+      <c r="H229" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -10513,10 +10502,10 @@
       <c r="F230" t="s">
         <v>12</v>
       </c>
-      <c r="G230" s="6" t="s">
+      <c r="G230" s="1" t="s">
         <v>833</v>
       </c>
-      <c r="H230" s="3" t="s">
+      <c r="H230" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -10539,10 +10528,10 @@
       <c r="F231" t="s">
         <v>43</v>
       </c>
-      <c r="G231" s="6" t="s">
+      <c r="G231" s="1" t="s">
         <v>836</v>
       </c>
-      <c r="H231" s="3" t="s">
+      <c r="H231" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -10565,10 +10554,10 @@
       <c r="F232" t="s">
         <v>34</v>
       </c>
-      <c r="G232" s="6" t="s">
+      <c r="G232" s="1" t="s">
         <v>840</v>
       </c>
-      <c r="H232" s="3" t="s">
+      <c r="H232" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -10591,10 +10580,10 @@
       <c r="F233" t="s">
         <v>24</v>
       </c>
-      <c r="G233" s="6" t="s">
+      <c r="G233" s="1" t="s">
         <v>844</v>
       </c>
-      <c r="H233" s="3" t="s">
+      <c r="H233" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -10617,10 +10606,10 @@
       <c r="F234" t="s">
         <v>12</v>
       </c>
-      <c r="G234" s="6" t="s">
+      <c r="G234" s="1" t="s">
         <v>848</v>
       </c>
-      <c r="H234" s="3" t="s">
+      <c r="H234" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -10643,7 +10632,7 @@
       <c r="F235" t="s">
         <v>12</v>
       </c>
-      <c r="G235" s="6" t="s">
+      <c r="G235" s="1" t="s">
         <v>849</v>
       </c>
       <c r="H235" s="4" t="s">
@@ -10669,11 +10658,11 @@
       <c r="F236" t="s">
         <v>12</v>
       </c>
-      <c r="G236" s="6" t="s">
+      <c r="G236" s="1" t="s">
         <v>852</v>
       </c>
       <c r="H236" s="4" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="237" spans="1:8" ht="32" x14ac:dyDescent="0.2">
@@ -10695,10 +10684,10 @@
       <c r="F237" t="s">
         <v>34</v>
       </c>
-      <c r="G237" s="6" t="s">
+      <c r="G237" s="1" t="s">
         <v>856</v>
       </c>
-      <c r="H237" s="3" t="s">
+      <c r="H237" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -10721,10 +10710,10 @@
       <c r="F238" t="s">
         <v>34</v>
       </c>
-      <c r="G238" s="6" t="s">
+      <c r="G238" s="1" t="s">
         <v>860</v>
       </c>
-      <c r="H238" s="3" t="s">
+      <c r="H238" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -10747,10 +10736,10 @@
       <c r="F239" t="s">
         <v>24</v>
       </c>
-      <c r="G239" s="6" t="s">
+      <c r="G239" s="1" t="s">
         <v>863</v>
       </c>
-      <c r="H239" s="3" t="s">
+      <c r="H239" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -10773,10 +10762,10 @@
       <c r="F240" t="s">
         <v>12</v>
       </c>
-      <c r="G240" s="6" t="s">
+      <c r="G240" s="1" t="s">
         <v>867</v>
       </c>
-      <c r="H240" s="3" t="s">
+      <c r="H240" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -10799,10 +10788,10 @@
       <c r="F241" t="s">
         <v>34</v>
       </c>
-      <c r="G241" s="6" t="s">
+      <c r="G241" s="1" t="s">
         <v>870</v>
       </c>
-      <c r="H241" s="3" t="s">
+      <c r="H241" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -10825,10 +10814,10 @@
       <c r="F242" t="s">
         <v>12</v>
       </c>
-      <c r="G242" s="6" t="s">
+      <c r="G242" s="1" t="s">
         <v>874</v>
       </c>
-      <c r="H242" s="3" t="s">
+      <c r="H242" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -10851,7 +10840,7 @@
       <c r="F243" t="s">
         <v>43</v>
       </c>
-      <c r="G243" s="6" t="s">
+      <c r="G243" s="1" t="s">
         <v>876</v>
       </c>
       <c r="H243" s="4" t="s">
@@ -10877,7 +10866,7 @@
       <c r="F244" t="s">
         <v>24</v>
       </c>
-      <c r="G244" s="6" t="s">
+      <c r="G244" s="1" t="s">
         <v>880</v>
       </c>
       <c r="H244" s="4" t="s">
@@ -10903,10 +10892,10 @@
       <c r="F245" t="s">
         <v>24</v>
       </c>
-      <c r="G245" s="6" t="s">
+      <c r="G245" s="1" t="s">
         <v>883</v>
       </c>
-      <c r="H245" s="3" t="s">
+      <c r="H245" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -10929,7 +10918,7 @@
       <c r="F246" t="s">
         <v>12</v>
       </c>
-      <c r="G246" s="6" t="s">
+      <c r="G246" s="1" t="s">
         <v>886</v>
       </c>
       <c r="H246" s="4" t="s">
@@ -10955,10 +10944,10 @@
       <c r="F247" t="s">
         <v>43</v>
       </c>
-      <c r="G247" s="6" t="s">
+      <c r="G247" s="1" t="s">
         <v>887</v>
       </c>
-      <c r="H247" s="3" t="s">
+      <c r="H247" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -10981,10 +10970,10 @@
       <c r="F248" t="s">
         <v>12</v>
       </c>
-      <c r="G248" s="6" t="s">
+      <c r="G248" s="1" t="s">
         <v>890</v>
       </c>
-      <c r="H248" s="3" t="s">
+      <c r="H248" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -11007,7 +10996,7 @@
       <c r="F249" t="s">
         <v>43</v>
       </c>
-      <c r="G249" s="6" t="s">
+      <c r="G249" s="1" t="s">
         <v>894</v>
       </c>
       <c r="H249" s="4" t="s">
@@ -11033,10 +11022,10 @@
       <c r="F250" t="s">
         <v>34</v>
       </c>
-      <c r="G250" s="6" t="s">
+      <c r="G250" s="1" t="s">
         <v>896</v>
       </c>
-      <c r="H250" s="3" t="s">
+      <c r="H250" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -11059,10 +11048,10 @@
       <c r="F251" t="s">
         <v>34</v>
       </c>
-      <c r="G251" s="6" t="s">
+      <c r="G251" s="1" t="s">
         <v>900</v>
       </c>
-      <c r="H251" s="3" t="s">
+      <c r="H251" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -11085,7 +11074,7 @@
       <c r="F252" t="s">
         <v>12</v>
       </c>
-      <c r="G252" s="6" t="s">
+      <c r="G252" s="1" t="s">
         <v>904</v>
       </c>
       <c r="H252" s="4" t="s">
@@ -11111,10 +11100,10 @@
       <c r="F253" t="s">
         <v>34</v>
       </c>
-      <c r="G253" s="6" t="s">
+      <c r="G253" s="1" t="s">
         <v>908</v>
       </c>
-      <c r="H253" s="3" t="s">
+      <c r="H253" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -11137,10 +11126,10 @@
       <c r="F254" t="s">
         <v>24</v>
       </c>
-      <c r="G254" s="6" t="s">
+      <c r="G254" s="1" t="s">
         <v>912</v>
       </c>
-      <c r="H254" s="2" t="s">
+      <c r="H254" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -11163,10 +11152,10 @@
       <c r="F255" t="s">
         <v>12</v>
       </c>
-      <c r="G255" s="6" t="s">
+      <c r="G255" s="1" t="s">
         <v>916</v>
       </c>
-      <c r="H255" s="3" t="s">
+      <c r="H255" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -11189,10 +11178,10 @@
       <c r="F256" t="s">
         <v>12</v>
       </c>
-      <c r="G256" s="6" t="s">
+      <c r="G256" s="1" t="s">
         <v>919</v>
       </c>
-      <c r="H256" s="3" t="s">
+      <c r="H256" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -11215,10 +11204,10 @@
       <c r="F257" t="s">
         <v>34</v>
       </c>
-      <c r="G257" s="6" t="s">
+      <c r="G257" s="1" t="s">
         <v>922</v>
       </c>
-      <c r="H257" s="3" t="s">
+      <c r="H257" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -11241,10 +11230,10 @@
       <c r="F258" t="s">
         <v>24</v>
       </c>
-      <c r="G258" s="6" t="s">
+      <c r="G258" s="1" t="s">
         <v>926</v>
       </c>
-      <c r="H258" s="3" t="s">
+      <c r="H258" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -11267,11 +11256,11 @@
       <c r="F259" t="s">
         <v>43</v>
       </c>
-      <c r="G259" s="6" t="s">
+      <c r="G259" s="1" t="s">
         <v>930</v>
       </c>
       <c r="H259" s="4" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="260" spans="1:8" ht="48" x14ac:dyDescent="0.2">
@@ -11293,7 +11282,7 @@
       <c r="F260" t="s">
         <v>34</v>
       </c>
-      <c r="G260" s="6" t="s">
+      <c r="G260" s="1" t="s">
         <v>933</v>
       </c>
       <c r="H260" s="4" t="s">
@@ -11319,11 +11308,11 @@
       <c r="F261" t="s">
         <v>12</v>
       </c>
-      <c r="G261" s="6" t="s">
+      <c r="G261" s="1" t="s">
         <v>936</v>
       </c>
-      <c r="H261" s="3" t="s">
-        <v>19</v>
+      <c r="H261" s="4" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="262" spans="1:8" ht="32" x14ac:dyDescent="0.2">
@@ -11345,10 +11334,10 @@
       <c r="F262" t="s">
         <v>34</v>
       </c>
-      <c r="G262" s="6" t="s">
+      <c r="G262" s="1" t="s">
         <v>940</v>
       </c>
-      <c r="H262" s="3" t="s">
+      <c r="H262" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -11371,10 +11360,10 @@
       <c r="F263" t="s">
         <v>34</v>
       </c>
-      <c r="G263" s="6" t="s">
+      <c r="G263" s="1" t="s">
         <v>944</v>
       </c>
-      <c r="H263" s="3" t="s">
+      <c r="H263" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -11397,7 +11386,7 @@
       <c r="F264" t="s">
         <v>24</v>
       </c>
-      <c r="G264" s="6" t="s">
+      <c r="G264" s="1" t="s">
         <v>946</v>
       </c>
       <c r="H264" s="4" t="s">
@@ -11423,7 +11412,7 @@
       <c r="F265" t="s">
         <v>24</v>
       </c>
-      <c r="G265" s="6" t="s">
+      <c r="G265" s="1" t="s">
         <v>949</v>
       </c>
       <c r="H265" s="4" t="s">
@@ -11449,10 +11438,10 @@
       <c r="F266" t="s">
         <v>24</v>
       </c>
-      <c r="G266" s="6" t="s">
+      <c r="G266" s="1" t="s">
         <v>952</v>
       </c>
-      <c r="H266" s="2" t="s">
+      <c r="H266" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -11475,10 +11464,10 @@
       <c r="F267" t="s">
         <v>24</v>
       </c>
-      <c r="G267" s="6" t="s">
+      <c r="G267" s="1" t="s">
         <v>956</v>
       </c>
-      <c r="H267" s="3" t="s">
+      <c r="H267" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -11501,10 +11490,10 @@
       <c r="F268" t="s">
         <v>24</v>
       </c>
-      <c r="G268" s="6" t="s">
+      <c r="G268" s="1" t="s">
         <v>959</v>
       </c>
-      <c r="H268" s="3" t="s">
+      <c r="H268" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -11527,10 +11516,10 @@
       <c r="F269" t="s">
         <v>24</v>
       </c>
-      <c r="G269" s="6" t="s">
+      <c r="G269" s="1" t="s">
         <v>962</v>
       </c>
-      <c r="H269" s="3" t="s">
+      <c r="H269" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -11553,10 +11542,10 @@
       <c r="F270" t="s">
         <v>24</v>
       </c>
-      <c r="G270" s="6" t="s">
+      <c r="G270" s="1" t="s">
         <v>966</v>
       </c>
-      <c r="H270" s="3" t="s">
+      <c r="H270" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -11579,10 +11568,10 @@
       <c r="F271" t="s">
         <v>43</v>
       </c>
-      <c r="G271" s="6" t="s">
+      <c r="G271" s="1" t="s">
         <v>969</v>
       </c>
-      <c r="H271" s="3" t="s">
+      <c r="H271" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -11605,10 +11594,10 @@
       <c r="F272" t="s">
         <v>43</v>
       </c>
-      <c r="G272" s="6" t="s">
+      <c r="G272" s="1" t="s">
         <v>973</v>
       </c>
-      <c r="H272" s="3" t="s">
+      <c r="H272" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -11631,10 +11620,10 @@
       <c r="F273" t="s">
         <v>43</v>
       </c>
-      <c r="G273" s="6" t="s">
+      <c r="G273" s="1" t="s">
         <v>976</v>
       </c>
-      <c r="H273" s="2" t="s">
+      <c r="H273" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -11657,10 +11646,10 @@
       <c r="F274" t="s">
         <v>24</v>
       </c>
-      <c r="G274" s="6" t="s">
+      <c r="G274" s="1" t="s">
         <v>980</v>
       </c>
-      <c r="H274" s="2" t="s">
+      <c r="H274" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -11683,10 +11672,10 @@
       <c r="F275" t="s">
         <v>24</v>
       </c>
-      <c r="G275" s="6" t="s">
+      <c r="G275" s="1" t="s">
         <v>983</v>
       </c>
-      <c r="H275" s="2" t="s">
+      <c r="H275" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -11709,7 +11698,7 @@
       <c r="F276" t="s">
         <v>24</v>
       </c>
-      <c r="G276" s="6" t="s">
+      <c r="G276" s="1" t="s">
         <v>987</v>
       </c>
       <c r="H276" s="4" t="s">
@@ -11735,10 +11724,10 @@
       <c r="F277" t="s">
         <v>34</v>
       </c>
-      <c r="G277" s="6" t="s">
+      <c r="G277" s="1" t="s">
         <v>990</v>
       </c>
-      <c r="H277" s="3" t="s">
+      <c r="H277" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -11761,10 +11750,10 @@
       <c r="F278" t="s">
         <v>24</v>
       </c>
-      <c r="G278" s="6" t="s">
+      <c r="G278" s="1" t="s">
         <v>994</v>
       </c>
-      <c r="H278" s="2" t="s">
+      <c r="H278" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -11787,10 +11776,10 @@
       <c r="F279" t="s">
         <v>12</v>
       </c>
-      <c r="G279" s="6" t="s">
+      <c r="G279" s="1" t="s">
         <v>998</v>
       </c>
-      <c r="H279" s="2" t="s">
+      <c r="H279" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -11813,10 +11802,10 @@
       <c r="F280" t="s">
         <v>34</v>
       </c>
-      <c r="G280" s="6" t="s">
+      <c r="G280" s="1" t="s">
         <v>1001</v>
       </c>
-      <c r="H280" s="2" t="s">
+      <c r="H280" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -11839,11 +11828,11 @@
       <c r="F281" t="s">
         <v>24</v>
       </c>
-      <c r="G281" s="6" t="s">
+      <c r="G281" s="1" t="s">
         <v>1004</v>
       </c>
-      <c r="H281" s="2" t="s">
-        <v>14</v>
+      <c r="H281" s="4" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="282" spans="1:8" ht="32" x14ac:dyDescent="0.2">
@@ -11865,10 +11854,10 @@
       <c r="F282" t="s">
         <v>24</v>
       </c>
-      <c r="G282" s="6" t="s">
+      <c r="G282" s="1" t="s">
         <v>1008</v>
       </c>
-      <c r="H282" s="2" t="s">
+      <c r="H282" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -11891,10 +11880,10 @@
       <c r="F283" t="s">
         <v>12</v>
       </c>
-      <c r="G283" s="6" t="s">
+      <c r="G283" s="1" t="s">
         <v>1011</v>
       </c>
-      <c r="H283" s="3" t="s">
+      <c r="H283" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -11917,10 +11906,10 @@
       <c r="F284" t="s">
         <v>12</v>
       </c>
-      <c r="G284" s="6" t="s">
+      <c r="G284" s="1" t="s">
         <v>1015</v>
       </c>
-      <c r="H284" s="3" t="s">
+      <c r="H284" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -11943,10 +11932,10 @@
       <c r="F285" t="s">
         <v>12</v>
       </c>
-      <c r="G285" s="6" t="s">
+      <c r="G285" s="1" t="s">
         <v>1016</v>
       </c>
-      <c r="H285" s="3" t="s">
+      <c r="H285" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -11969,10 +11958,10 @@
       <c r="F286" t="s">
         <v>34</v>
       </c>
-      <c r="G286" s="6" t="s">
+      <c r="G286" s="1" t="s">
         <v>1020</v>
       </c>
-      <c r="H286" s="3" t="s">
+      <c r="H286" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -11995,10 +11984,10 @@
       <c r="F287" t="s">
         <v>12</v>
       </c>
-      <c r="G287" s="6" t="s">
+      <c r="G287" s="1" t="s">
         <v>1024</v>
       </c>
-      <c r="H287" s="3" t="s">
+      <c r="H287" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -12021,10 +12010,10 @@
       <c r="F288" t="s">
         <v>12</v>
       </c>
-      <c r="G288" s="6" t="s">
+      <c r="G288" s="1" t="s">
         <v>1027</v>
       </c>
-      <c r="H288" s="3" t="s">
+      <c r="H288" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -12047,10 +12036,10 @@
       <c r="F289" t="s">
         <v>43</v>
       </c>
-      <c r="G289" s="6" t="s">
+      <c r="G289" s="1" t="s">
         <v>1030</v>
       </c>
-      <c r="H289" s="2" t="s">
+      <c r="H289" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -12073,10 +12062,10 @@
       <c r="F290" t="s">
         <v>12</v>
       </c>
-      <c r="G290" s="6" t="s">
+      <c r="G290" s="1" t="s">
         <v>1033</v>
       </c>
-      <c r="H290" s="3" t="s">
+      <c r="H290" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -12099,10 +12088,10 @@
       <c r="F291" t="s">
         <v>12</v>
       </c>
-      <c r="G291" s="6" t="s">
+      <c r="G291" s="1" t="s">
         <v>1034</v>
       </c>
-      <c r="H291" s="3" t="s">
+      <c r="H291" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -12125,7 +12114,7 @@
       <c r="F292" t="s">
         <v>24</v>
       </c>
-      <c r="G292" s="6" t="s">
+      <c r="G292" s="1" t="s">
         <v>1038</v>
       </c>
       <c r="H292" s="4" t="s">
@@ -12151,10 +12140,10 @@
       <c r="F293" t="s">
         <v>12</v>
       </c>
-      <c r="G293" s="6" t="s">
+      <c r="G293" s="1" t="s">
         <v>1041</v>
       </c>
-      <c r="H293" s="3" t="s">
+      <c r="H293" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -12177,7 +12166,7 @@
       <c r="F294" t="s">
         <v>24</v>
       </c>
-      <c r="G294" s="6" t="s">
+      <c r="G294" s="1" t="s">
         <v>1043</v>
       </c>
       <c r="H294" s="4" t="s">
@@ -12203,10 +12192,10 @@
       <c r="F295" t="s">
         <v>12</v>
       </c>
-      <c r="G295" s="6" t="s">
+      <c r="G295" s="1" t="s">
         <v>1044</v>
       </c>
-      <c r="H295" s="3" t="s">
+      <c r="H295" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -12229,10 +12218,10 @@
       <c r="F296" t="s">
         <v>12</v>
       </c>
-      <c r="G296" s="6" t="s">
+      <c r="G296" s="1" t="s">
         <v>1047</v>
       </c>
-      <c r="H296" s="3" t="s">
+      <c r="H296" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -12255,10 +12244,10 @@
       <c r="F297" t="s">
         <v>24</v>
       </c>
-      <c r="G297" s="6" t="s">
+      <c r="G297" s="1" t="s">
         <v>1051</v>
       </c>
-      <c r="H297" s="3" t="s">
+      <c r="H297" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -12281,10 +12270,10 @@
       <c r="F298" t="s">
         <v>12</v>
       </c>
-      <c r="G298" s="6" t="s">
+      <c r="G298" s="1" t="s">
         <v>1052</v>
       </c>
-      <c r="H298" s="3" t="s">
+      <c r="H298" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -12307,10 +12296,10 @@
       <c r="F299" t="s">
         <v>12</v>
       </c>
-      <c r="G299" s="6" t="s">
+      <c r="G299" s="1" t="s">
         <v>1054</v>
       </c>
-      <c r="H299" s="3" t="s">
+      <c r="H299" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -12333,10 +12322,10 @@
       <c r="F300" t="s">
         <v>12</v>
       </c>
-      <c r="G300" s="6" t="s">
+      <c r="G300" s="1" t="s">
         <v>1057</v>
       </c>
-      <c r="H300" s="3" t="s">
+      <c r="H300" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -12359,10 +12348,10 @@
       <c r="F301" t="s">
         <v>12</v>
       </c>
-      <c r="G301" s="6" t="s">
+      <c r="G301" s="1" t="s">
         <v>1061</v>
       </c>
-      <c r="H301" s="3" t="s">
+      <c r="H301" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -12385,10 +12374,10 @@
       <c r="F302" t="s">
         <v>34</v>
       </c>
-      <c r="G302" s="6" t="s">
+      <c r="G302" s="1" t="s">
         <v>1065</v>
       </c>
-      <c r="H302" s="3" t="s">
+      <c r="H302" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -12411,10 +12400,10 @@
       <c r="F303" t="s">
         <v>43</v>
       </c>
-      <c r="G303" s="6" t="s">
+      <c r="G303" s="1" t="s">
         <v>1068</v>
       </c>
-      <c r="H303" s="3" t="s">
+      <c r="H303" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -12437,10 +12426,10 @@
       <c r="F304" t="s">
         <v>24</v>
       </c>
-      <c r="G304" s="6" t="s">
+      <c r="G304" s="1" t="s">
         <v>1072</v>
       </c>
-      <c r="H304" s="3" t="s">
+      <c r="H304" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -12463,10 +12452,10 @@
       <c r="F305" t="s">
         <v>34</v>
       </c>
-      <c r="G305" s="6" t="s">
+      <c r="G305" s="1" t="s">
         <v>1074</v>
       </c>
-      <c r="H305" s="2" t="s">
+      <c r="H305" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -12489,11 +12478,11 @@
       <c r="F306" t="s">
         <v>12</v>
       </c>
-      <c r="G306" s="6" t="s">
+      <c r="G306" s="1" t="s">
         <v>1076</v>
       </c>
-      <c r="H306" s="3" t="s">
-        <v>19</v>
+      <c r="H306" s="4" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="307" spans="1:8" ht="48" x14ac:dyDescent="0.2">
@@ -12515,10 +12504,10 @@
       <c r="F307" t="s">
         <v>12</v>
       </c>
-      <c r="G307" s="6" t="s">
+      <c r="G307" s="1" t="s">
         <v>1079</v>
       </c>
-      <c r="H307" s="2" t="s">
+      <c r="H307" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -12541,7 +12530,7 @@
       <c r="F308" t="s">
         <v>43</v>
       </c>
-      <c r="G308" s="6" t="s">
+      <c r="G308" s="1" t="s">
         <v>1083</v>
       </c>
       <c r="H308" s="4" t="s">
@@ -12567,10 +12556,10 @@
       <c r="F309" t="s">
         <v>12</v>
       </c>
-      <c r="G309" s="6" t="s">
+      <c r="G309" s="1" t="s">
         <v>1086</v>
       </c>
-      <c r="H309" s="3" t="s">
+      <c r="H309" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -12593,10 +12582,10 @@
       <c r="F310" t="s">
         <v>34</v>
       </c>
-      <c r="G310" s="6" t="s">
+      <c r="G310" s="1" t="s">
         <v>1089</v>
       </c>
-      <c r="H310" s="3" t="s">
+      <c r="H310" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -12619,10 +12608,10 @@
       <c r="F311" t="s">
         <v>12</v>
       </c>
-      <c r="G311" s="6" t="s">
+      <c r="G311" s="1" t="s">
         <v>1093</v>
       </c>
-      <c r="H311" s="3" t="s">
+      <c r="H311" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -12645,10 +12634,10 @@
       <c r="F312" t="s">
         <v>43</v>
       </c>
-      <c r="G312" s="6" t="s">
+      <c r="G312" s="1" t="s">
         <v>1096</v>
       </c>
-      <c r="H312" s="3" t="s">
+      <c r="H312" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -12671,10 +12660,10 @@
       <c r="F313" t="s">
         <v>43</v>
       </c>
-      <c r="G313" s="6" t="s">
+      <c r="G313" s="1" t="s">
         <v>1100</v>
       </c>
-      <c r="H313" s="2" t="s">
+      <c r="H313" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -12697,10 +12686,10 @@
       <c r="F314" t="s">
         <v>43</v>
       </c>
-      <c r="G314" s="6" t="s">
+      <c r="G314" s="1" t="s">
         <v>1101</v>
       </c>
-      <c r="H314" s="3" t="s">
+      <c r="H314" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -12723,10 +12712,10 @@
       <c r="F315" t="s">
         <v>12</v>
       </c>
-      <c r="G315" s="6" t="s">
+      <c r="G315" s="1" t="s">
         <v>1104</v>
       </c>
-      <c r="H315" s="3" t="s">
+      <c r="H315" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -12749,10 +12738,10 @@
       <c r="F316" t="s">
         <v>43</v>
       </c>
-      <c r="G316" s="6" t="s">
+      <c r="G316" s="1" t="s">
         <v>1108</v>
       </c>
-      <c r="H316" s="3" t="s">
+      <c r="H316" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -12775,10 +12764,10 @@
       <c r="F317" t="s">
         <v>12</v>
       </c>
-      <c r="G317" s="6" t="s">
+      <c r="G317" s="1" t="s">
         <v>1111</v>
       </c>
-      <c r="H317" s="3" t="s">
+      <c r="H317" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -12801,10 +12790,10 @@
       <c r="F318" t="s">
         <v>12</v>
       </c>
-      <c r="G318" s="6" t="s">
+      <c r="G318" s="1" t="s">
         <v>1113</v>
       </c>
-      <c r="H318" s="3" t="s">
+      <c r="H318" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -12827,10 +12816,10 @@
       <c r="F319" t="s">
         <v>12</v>
       </c>
-      <c r="G319" s="6" t="s">
+      <c r="G319" s="1" t="s">
         <v>1115</v>
       </c>
-      <c r="H319" s="2" t="s">
+      <c r="H319" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -12853,10 +12842,10 @@
       <c r="F320" t="s">
         <v>12</v>
       </c>
-      <c r="G320" s="6" t="s">
+      <c r="G320" s="1" t="s">
         <v>1118</v>
       </c>
-      <c r="H320" s="3" t="s">
+      <c r="H320" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -12879,10 +12868,10 @@
       <c r="F321" t="s">
         <v>34</v>
       </c>
-      <c r="G321" s="6" t="s">
+      <c r="G321" s="1" t="s">
         <v>1121</v>
       </c>
-      <c r="H321" s="2" t="s">
+      <c r="H321" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -12905,10 +12894,10 @@
       <c r="F322" t="s">
         <v>43</v>
       </c>
-      <c r="G322" s="6" t="s">
+      <c r="G322" s="1" t="s">
         <v>1124</v>
       </c>
-      <c r="H322" s="3" t="s">
+      <c r="H322" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -12931,10 +12920,10 @@
       <c r="F323" t="s">
         <v>34</v>
       </c>
-      <c r="G323" s="6" t="s">
+      <c r="G323" s="1" t="s">
         <v>1128</v>
       </c>
-      <c r="H323" s="3" t="s">
+      <c r="H323" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -12957,11 +12946,11 @@
       <c r="F324" t="s">
         <v>12</v>
       </c>
-      <c r="G324" s="6" t="s">
+      <c r="G324" s="1" t="s">
         <v>1132</v>
       </c>
       <c r="H324" s="4" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="325" spans="1:8" ht="128" x14ac:dyDescent="0.2">
@@ -12983,10 +12972,10 @@
       <c r="F325" t="s">
         <v>34</v>
       </c>
-      <c r="G325" s="6" t="s">
+      <c r="G325" s="1" t="s">
         <v>1135</v>
       </c>
-      <c r="H325" s="3" t="s">
+      <c r="H325" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -13009,11 +12998,11 @@
       <c r="F326" t="s">
         <v>24</v>
       </c>
-      <c r="G326" s="6" t="s">
+      <c r="G326" s="1" t="s">
         <v>1139</v>
       </c>
       <c r="H326" s="4" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="327" spans="1:8" ht="48" x14ac:dyDescent="0.2">
@@ -13035,10 +13024,10 @@
       <c r="F327" t="s">
         <v>34</v>
       </c>
-      <c r="G327" s="6" t="s">
+      <c r="G327" s="1" t="s">
         <v>1142</v>
       </c>
-      <c r="H327" s="3" t="s">
+      <c r="H327" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -13061,10 +13050,10 @@
       <c r="F328" t="s">
         <v>12</v>
       </c>
-      <c r="G328" s="6" t="s">
+      <c r="G328" s="1" t="s">
         <v>1143</v>
       </c>
-      <c r="H328" s="3" t="s">
+      <c r="H328" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -13087,10 +13076,10 @@
       <c r="F329" t="s">
         <v>12</v>
       </c>
-      <c r="G329" s="6" t="s">
+      <c r="G329" s="1" t="s">
         <v>1147</v>
       </c>
-      <c r="H329" s="3" t="s">
+      <c r="H329" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -13113,10 +13102,10 @@
       <c r="F330" t="s">
         <v>43</v>
       </c>
-      <c r="G330" s="6" t="s">
+      <c r="G330" s="1" t="s">
         <v>1150</v>
       </c>
-      <c r="H330" s="2" t="s">
+      <c r="H330" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -13139,10 +13128,10 @@
       <c r="F331" t="s">
         <v>34</v>
       </c>
-      <c r="G331" s="6" t="s">
+      <c r="G331" s="1" t="s">
         <v>1153</v>
       </c>
-      <c r="H331" s="3" t="s">
+      <c r="H331" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -13165,10 +13154,10 @@
       <c r="F332" t="s">
         <v>34</v>
       </c>
-      <c r="G332" s="6" t="s">
+      <c r="G332" s="1" t="s">
         <v>1156</v>
       </c>
-      <c r="H332" s="3" t="s">
+      <c r="H332" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -13191,7 +13180,7 @@
       <c r="F333" t="s">
         <v>12</v>
       </c>
-      <c r="G333" s="6" t="s">
+      <c r="G333" s="1" t="s">
         <v>1159</v>
       </c>
       <c r="H333" s="4" t="s">
@@ -13217,10 +13206,10 @@
       <c r="F334" t="s">
         <v>24</v>
       </c>
-      <c r="G334" s="6" t="s">
+      <c r="G334" s="1" t="s">
         <v>1163</v>
       </c>
-      <c r="H334" s="2" t="s">
+      <c r="H334" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -13243,10 +13232,10 @@
       <c r="F335" t="s">
         <v>12</v>
       </c>
-      <c r="G335" s="6" t="s">
+      <c r="G335" s="1" t="s">
         <v>1166</v>
       </c>
-      <c r="H335" s="3" t="s">
+      <c r="H335" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -13269,10 +13258,10 @@
       <c r="F336" t="s">
         <v>43</v>
       </c>
-      <c r="G336" s="6" t="s">
+      <c r="G336" s="1" t="s">
         <v>1169</v>
       </c>
-      <c r="H336" s="3" t="s">
+      <c r="H336" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -13295,10 +13284,10 @@
       <c r="F337" t="s">
         <v>24</v>
       </c>
-      <c r="G337" s="6" t="s">
+      <c r="G337" s="1" t="s">
         <v>1171</v>
       </c>
-      <c r="H337" s="3" t="s">
+      <c r="H337" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -13321,7 +13310,7 @@
       <c r="F338" t="s">
         <v>24</v>
       </c>
-      <c r="G338" s="6" t="s">
+      <c r="G338" s="1" t="s">
         <v>1174</v>
       </c>
       <c r="H338" s="4" t="s">
@@ -13347,10 +13336,10 @@
       <c r="F339" t="s">
         <v>12</v>
       </c>
-      <c r="G339" s="6" t="s">
+      <c r="G339" s="1" t="s">
         <v>1176</v>
       </c>
-      <c r="H339" s="3" t="s">
+      <c r="H339" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -13373,7 +13362,7 @@
       <c r="F340" t="s">
         <v>12</v>
       </c>
-      <c r="G340" s="6" t="s">
+      <c r="G340" s="1" t="s">
         <v>1178</v>
       </c>
       <c r="H340" s="4" t="s">
@@ -13399,10 +13388,10 @@
       <c r="F341" t="s">
         <v>12</v>
       </c>
-      <c r="G341" s="6" t="s">
+      <c r="G341" s="1" t="s">
         <v>1181</v>
       </c>
-      <c r="H341" s="3" t="s">
+      <c r="H341" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -13425,10 +13414,10 @@
       <c r="F342" t="s">
         <v>34</v>
       </c>
-      <c r="G342" s="6" t="s">
+      <c r="G342" s="1" t="s">
         <v>1184</v>
       </c>
-      <c r="H342" s="2" t="s">
+      <c r="H342" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -13451,11 +13440,11 @@
       <c r="F343" t="s">
         <v>24</v>
       </c>
-      <c r="G343" s="6" t="s">
+      <c r="G343" s="1" t="s">
         <v>1187</v>
       </c>
       <c r="H343" s="4" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="344" spans="1:8" ht="32" x14ac:dyDescent="0.2">
@@ -13477,10 +13466,10 @@
       <c r="F344" t="s">
         <v>12</v>
       </c>
-      <c r="G344" s="6" t="s">
+      <c r="G344" s="1" t="s">
         <v>1189</v>
       </c>
-      <c r="H344" s="2" t="s">
+      <c r="H344" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -13503,10 +13492,10 @@
       <c r="F345" t="s">
         <v>12</v>
       </c>
-      <c r="G345" s="6" t="s">
+      <c r="G345" s="1" t="s">
         <v>1191</v>
       </c>
-      <c r="H345" s="3" t="s">
+      <c r="H345" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -13529,10 +13518,10 @@
       <c r="F346" t="s">
         <v>12</v>
       </c>
-      <c r="G346" s="6" t="s">
+      <c r="G346" s="1" t="s">
         <v>1195</v>
       </c>
-      <c r="H346" s="3" t="s">
+      <c r="H346" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -13555,10 +13544,10 @@
       <c r="F347" t="s">
         <v>43</v>
       </c>
-      <c r="G347" s="6" t="s">
+      <c r="G347" s="1" t="s">
         <v>1198</v>
       </c>
-      <c r="H347" s="3" t="s">
+      <c r="H347" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -13581,10 +13570,10 @@
       <c r="F348" t="s">
         <v>12</v>
       </c>
-      <c r="G348" s="6" t="s">
+      <c r="G348" s="1" t="s">
         <v>1201</v>
       </c>
-      <c r="H348" s="3" t="s">
+      <c r="H348" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -13607,11 +13596,11 @@
       <c r="F349" t="s">
         <v>12</v>
       </c>
-      <c r="G349" s="6" t="s">
+      <c r="G349" s="1" t="s">
         <v>1205</v>
       </c>
-      <c r="H349" s="2" t="s">
-        <v>14</v>
+      <c r="H349" s="4" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="350" spans="1:8" ht="32" x14ac:dyDescent="0.2">
@@ -13633,10 +13622,10 @@
       <c r="F350" t="s">
         <v>43</v>
       </c>
-      <c r="G350" s="6" t="s">
+      <c r="G350" s="1" t="s">
         <v>1209</v>
       </c>
-      <c r="H350" s="3" t="s">
+      <c r="H350" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -13659,10 +13648,10 @@
       <c r="F351" t="s">
         <v>12</v>
       </c>
-      <c r="G351" s="6" t="s">
+      <c r="G351" s="1" t="s">
         <v>1212</v>
       </c>
-      <c r="H351" s="3" t="s">
+      <c r="H351" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -13685,10 +13674,10 @@
       <c r="F352" t="s">
         <v>43</v>
       </c>
-      <c r="G352" s="6" t="s">
+      <c r="G352" s="1" t="s">
         <v>1215</v>
       </c>
-      <c r="H352" s="3" t="s">
+      <c r="H352" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -13711,7 +13700,7 @@
       <c r="F353" t="s">
         <v>24</v>
       </c>
-      <c r="G353" s="6" t="s">
+      <c r="G353" s="1" t="s">
         <v>1219</v>
       </c>
       <c r="H353" s="4" t="s">
@@ -13737,10 +13726,10 @@
       <c r="F354" t="s">
         <v>34</v>
       </c>
-      <c r="G354" s="6" t="s">
+      <c r="G354" s="1" t="s">
         <v>1223</v>
       </c>
-      <c r="H354" s="3" t="s">
+      <c r="H354" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -13763,10 +13752,10 @@
       <c r="F355" t="s">
         <v>12</v>
       </c>
-      <c r="G355" s="6" t="s">
+      <c r="G355" s="1" t="s">
         <v>1227</v>
       </c>
-      <c r="H355" s="3" t="s">
+      <c r="H355" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -13789,10 +13778,10 @@
       <c r="F356" t="s">
         <v>24</v>
       </c>
-      <c r="G356" s="6" t="s">
+      <c r="G356" s="1" t="s">
         <v>1230</v>
       </c>
-      <c r="H356" s="2" t="s">
+      <c r="H356" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -13815,10 +13804,10 @@
       <c r="F357" t="s">
         <v>34</v>
       </c>
-      <c r="G357" s="6" t="s">
+      <c r="G357" s="1" t="s">
         <v>1233</v>
       </c>
-      <c r="H357" s="3" t="s">
+      <c r="H357" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -13841,10 +13830,10 @@
       <c r="F358" t="s">
         <v>43</v>
       </c>
-      <c r="G358" s="6" t="s">
+      <c r="G358" s="1" t="s">
         <v>1236</v>
       </c>
-      <c r="H358" s="3" t="s">
+      <c r="H358" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -13867,10 +13856,10 @@
       <c r="F359" t="s">
         <v>12</v>
       </c>
-      <c r="G359" s="6" t="s">
+      <c r="G359" s="1" t="s">
         <v>1239</v>
       </c>
-      <c r="H359" s="3" t="s">
+      <c r="H359" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -13893,10 +13882,10 @@
       <c r="F360" t="s">
         <v>43</v>
       </c>
-      <c r="G360" s="6" t="s">
+      <c r="G360" s="1" t="s">
         <v>1242</v>
       </c>
-      <c r="H360" s="3" t="s">
+      <c r="H360" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -13919,10 +13908,10 @@
       <c r="F361" t="s">
         <v>24</v>
       </c>
-      <c r="G361" s="6" t="s">
+      <c r="G361" s="1" t="s">
         <v>1246</v>
       </c>
-      <c r="H361" s="3" t="s">
+      <c r="H361" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -13945,10 +13934,10 @@
       <c r="F362" t="s">
         <v>24</v>
       </c>
-      <c r="G362" s="6" t="s">
+      <c r="G362" s="1" t="s">
         <v>1249</v>
       </c>
-      <c r="H362" s="2" t="s">
+      <c r="H362" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -13971,7 +13960,7 @@
       <c r="F363" t="s">
         <v>24</v>
       </c>
-      <c r="G363" s="6" t="s">
+      <c r="G363" s="1" t="s">
         <v>1252</v>
       </c>
       <c r="H363" s="4" t="s">
@@ -13997,10 +13986,10 @@
       <c r="F364" t="s">
         <v>12</v>
       </c>
-      <c r="G364" s="6" t="s">
+      <c r="G364" s="1" t="s">
         <v>1255</v>
       </c>
-      <c r="H364" s="3" t="s">
+      <c r="H364" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -14023,11 +14012,11 @@
       <c r="F365" t="s">
         <v>24</v>
       </c>
-      <c r="G365" s="6" t="s">
+      <c r="G365" s="1" t="s">
         <v>1259</v>
       </c>
       <c r="H365" s="4" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="366" spans="1:8" ht="32" x14ac:dyDescent="0.2">
@@ -14049,10 +14038,10 @@
       <c r="F366" t="s">
         <v>12</v>
       </c>
-      <c r="G366" s="6" t="s">
+      <c r="G366" s="1" t="s">
         <v>1263</v>
       </c>
-      <c r="H366" s="3" t="s">
+      <c r="H366" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -14075,10 +14064,10 @@
       <c r="F367" t="s">
         <v>34</v>
       </c>
-      <c r="G367" s="6" t="s">
+      <c r="G367" s="1" t="s">
         <v>1265</v>
       </c>
-      <c r="H367" s="3" t="s">
+      <c r="H367" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -14101,11 +14090,11 @@
       <c r="F368" t="s">
         <v>24</v>
       </c>
-      <c r="G368" s="6" t="s">
+      <c r="G368" s="1" t="s">
         <v>1268</v>
       </c>
-      <c r="H368" s="3" t="s">
-        <v>19</v>
+      <c r="H368" s="4" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="369" spans="1:8" ht="16" x14ac:dyDescent="0.2">
@@ -14127,10 +14116,10 @@
       <c r="F369" t="s">
         <v>12</v>
       </c>
-      <c r="G369" s="6" t="s">
+      <c r="G369" s="1" t="s">
         <v>1271</v>
       </c>
-      <c r="H369" s="3" t="s">
+      <c r="H369" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -14153,10 +14142,10 @@
       <c r="F370" t="s">
         <v>43</v>
       </c>
-      <c r="G370" s="6" t="s">
+      <c r="G370" s="1" t="s">
         <v>1275</v>
       </c>
-      <c r="H370" s="3" t="s">
+      <c r="H370" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -14179,10 +14168,10 @@
       <c r="F371" t="s">
         <v>43</v>
       </c>
-      <c r="G371" s="6" t="s">
+      <c r="G371" s="1" t="s">
         <v>1278</v>
       </c>
-      <c r="H371" s="3" t="s">
+      <c r="H371" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -14205,10 +14194,10 @@
       <c r="F372" t="s">
         <v>34</v>
       </c>
-      <c r="G372" s="6" t="s">
+      <c r="G372" s="1" t="s">
         <v>1281</v>
       </c>
-      <c r="H372" s="3" t="s">
+      <c r="H372" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -14231,10 +14220,10 @@
       <c r="F373" t="s">
         <v>24</v>
       </c>
-      <c r="G373" s="6" t="s">
+      <c r="G373" s="1" t="s">
         <v>1285</v>
       </c>
-      <c r="H373" s="2" t="s">
+      <c r="H373" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -14257,10 +14246,10 @@
       <c r="F374" t="s">
         <v>24</v>
       </c>
-      <c r="G374" s="6" t="s">
+      <c r="G374" s="1" t="s">
         <v>1287</v>
       </c>
-      <c r="H374" s="2" t="s">
+      <c r="H374" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -14283,10 +14272,10 @@
       <c r="F375" t="s">
         <v>12</v>
       </c>
-      <c r="G375" s="6" t="s">
+      <c r="G375" s="1" t="s">
         <v>1289</v>
       </c>
-      <c r="H375" s="3" t="s">
+      <c r="H375" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -14309,10 +14298,10 @@
       <c r="F376" t="s">
         <v>12</v>
       </c>
-      <c r="G376" s="6" t="s">
+      <c r="G376" s="1" t="s">
         <v>1292</v>
       </c>
-      <c r="H376" s="3" t="s">
+      <c r="H376" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -14335,10 +14324,10 @@
       <c r="F377" t="s">
         <v>12</v>
       </c>
-      <c r="G377" s="6" t="s">
+      <c r="G377" s="1" t="s">
         <v>1295</v>
       </c>
-      <c r="H377" s="3" t="s">
+      <c r="H377" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -14361,10 +14350,10 @@
       <c r="F378" t="s">
         <v>12</v>
       </c>
-      <c r="G378" s="6" t="s">
+      <c r="G378" s="1" t="s">
         <v>1297</v>
       </c>
-      <c r="H378" s="3" t="s">
+      <c r="H378" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -14387,10 +14376,10 @@
       <c r="F379" t="s">
         <v>12</v>
       </c>
-      <c r="G379" s="6" t="s">
+      <c r="G379" s="1" t="s">
         <v>1301</v>
       </c>
-      <c r="H379" s="3" t="s">
+      <c r="H379" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -14413,10 +14402,10 @@
       <c r="F380" t="s">
         <v>12</v>
       </c>
-      <c r="G380" s="6" t="s">
+      <c r="G380" s="1" t="s">
         <v>1303</v>
       </c>
-      <c r="H380" s="3" t="s">
+      <c r="H380" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -14439,10 +14428,10 @@
       <c r="F381" t="s">
         <v>12</v>
       </c>
-      <c r="G381" s="6" t="s">
+      <c r="G381" s="1" t="s">
         <v>1306</v>
       </c>
-      <c r="H381" s="3" t="s">
+      <c r="H381" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -14465,11 +14454,11 @@
       <c r="F382" t="s">
         <v>34</v>
       </c>
-      <c r="G382" s="6" t="s">
+      <c r="G382" s="1" t="s">
         <v>1309</v>
       </c>
       <c r="H382" s="4" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="383" spans="1:8" ht="16" x14ac:dyDescent="0.2">
@@ -14491,10 +14480,10 @@
       <c r="F383" t="s">
         <v>12</v>
       </c>
-      <c r="G383" s="6" t="s">
+      <c r="G383" s="1" t="s">
         <v>1312</v>
       </c>
-      <c r="H383" s="3" t="s">
+      <c r="H383" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -14517,10 +14506,10 @@
       <c r="F384" t="s">
         <v>12</v>
       </c>
-      <c r="G384" s="6" t="s">
+      <c r="G384" s="1" t="s">
         <v>1316</v>
       </c>
-      <c r="H384" s="3" t="s">
+      <c r="H384" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -14543,7 +14532,7 @@
       <c r="F385" t="s">
         <v>34</v>
       </c>
-      <c r="G385" s="6" t="s">
+      <c r="G385" s="1" t="s">
         <v>1319</v>
       </c>
       <c r="H385" s="4" t="s">
@@ -14569,10 +14558,10 @@
       <c r="F386" t="s">
         <v>24</v>
       </c>
-      <c r="G386" s="6" t="s">
+      <c r="G386" s="1" t="s">
         <v>1322</v>
       </c>
-      <c r="H386" s="2" t="s">
+      <c r="H386" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -14595,10 +14584,10 @@
       <c r="F387" t="s">
         <v>34</v>
       </c>
-      <c r="G387" s="6" t="s">
+      <c r="G387" s="1" t="s">
         <v>1324</v>
       </c>
-      <c r="H387" s="3" t="s">
+      <c r="H387" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -14621,7 +14610,7 @@
       <c r="F388" t="s">
         <v>12</v>
       </c>
-      <c r="G388" s="6" t="s">
+      <c r="G388" s="1" t="s">
         <v>1326</v>
       </c>
       <c r="H388" s="4" t="s">
@@ -14647,10 +14636,10 @@
       <c r="F389" t="s">
         <v>12</v>
       </c>
-      <c r="G389" s="6" t="s">
+      <c r="G389" s="1" t="s">
         <v>1329</v>
       </c>
-      <c r="H389" s="3" t="s">
+      <c r="H389" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -14673,10 +14662,10 @@
       <c r="F390" t="s">
         <v>43</v>
       </c>
-      <c r="G390" s="6" t="s">
+      <c r="G390" s="1" t="s">
         <v>1333</v>
       </c>
-      <c r="H390" s="3" t="s">
+      <c r="H390" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -14699,10 +14688,10 @@
       <c r="F391" t="s">
         <v>43</v>
       </c>
-      <c r="G391" s="6" t="s">
+      <c r="G391" s="1" t="s">
         <v>1336</v>
       </c>
-      <c r="H391" s="3" t="s">
+      <c r="H391" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -14725,10 +14714,10 @@
       <c r="F392" t="s">
         <v>12</v>
       </c>
-      <c r="G392" s="6" t="s">
+      <c r="G392" s="1" t="s">
         <v>1339</v>
       </c>
-      <c r="H392" s="3" t="s">
+      <c r="H392" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -14751,7 +14740,7 @@
       <c r="F393" t="s">
         <v>43</v>
       </c>
-      <c r="G393" s="6" t="s">
+      <c r="G393" s="1" t="s">
         <v>1342</v>
       </c>
       <c r="H393" s="4" t="s">
@@ -14777,10 +14766,10 @@
       <c r="F394" t="s">
         <v>24</v>
       </c>
-      <c r="G394" s="6" t="s">
+      <c r="G394" s="1" t="s">
         <v>1345</v>
       </c>
-      <c r="H394" s="3" t="s">
+      <c r="H394" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -14803,7 +14792,7 @@
       <c r="F395" t="s">
         <v>43</v>
       </c>
-      <c r="G395" s="6" t="s">
+      <c r="G395" s="1" t="s">
         <v>1348</v>
       </c>
       <c r="H395" s="4" t="s">
@@ -14829,11 +14818,11 @@
       <c r="F396" t="s">
         <v>34</v>
       </c>
-      <c r="G396" s="6" t="s">
+      <c r="G396" s="1" t="s">
         <v>1351</v>
       </c>
       <c r="H396" s="4" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="397" spans="1:8" ht="48" x14ac:dyDescent="0.2">
@@ -14855,7 +14844,7 @@
       <c r="F397" t="s">
         <v>12</v>
       </c>
-      <c r="G397" s="6" t="s">
+      <c r="G397" s="1" t="s">
         <v>1354</v>
       </c>
       <c r="H397" s="4" t="s">
@@ -14881,10 +14870,10 @@
       <c r="F398" t="s">
         <v>34</v>
       </c>
-      <c r="G398" s="6" t="s">
+      <c r="G398" s="1" t="s">
         <v>1357</v>
       </c>
-      <c r="H398" s="3" t="s">
+      <c r="H398" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -14907,10 +14896,10 @@
       <c r="F399" t="s">
         <v>34</v>
       </c>
-      <c r="G399" s="6" t="s">
+      <c r="G399" s="1" t="s">
         <v>1360</v>
       </c>
-      <c r="H399" s="3" t="s">
+      <c r="H399" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -14933,10 +14922,10 @@
       <c r="F400" t="s">
         <v>12</v>
       </c>
-      <c r="G400" s="6" t="s">
+      <c r="G400" s="1" t="s">
         <v>1364</v>
       </c>
-      <c r="H400" s="3" t="s">
+      <c r="H400" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -14959,10 +14948,10 @@
       <c r="F401" t="s">
         <v>12</v>
       </c>
-      <c r="G401" s="6" t="s">
+      <c r="G401" s="1" t="s">
         <v>1368</v>
       </c>
-      <c r="H401" s="3" t="s">
+      <c r="H401" s="4" t="s">
         <v>19</v>
       </c>
     </row>
